--- a/veepee/Veepee - stock disponible vente privee.xlsx
+++ b/veepee/Veepee - stock disponible vente privee.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stock Veepee" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock Veepee'!$A$1:$T$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock Veepee'!$A$1:$S$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +37,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3A5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,7 +62,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -82,18 +77,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -462,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T68"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -470,21 +453,20 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
     <col width="45" customWidth="1" min="16" max="16"/>
     <col width="40" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -515,54 +497,54 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Saveurs FR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Saveurs NL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Qté dispo</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>DLU la plus proche</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Prix TTC</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Prix de vente conseillé TTC (RRP)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>TVA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Prix HTVA</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>RRP HTVA</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Prix Veepee TTC (−40 %)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Prix Veepee HTVA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>URL photo</t>
@@ -581,11 +563,6 @@
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Description NL</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Remarque</t>
         </is>
       </c>
     </row>
@@ -615,41 +592,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — pomme, citron, vanille</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — appel, citroen, vanille</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>27/12/2027</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="K2" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="L2" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="M2" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="N2" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="O2" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O2" s="4" t="n">
-        <v>11.5</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -701,7 +676,6 @@
 Kinderen zijn dol op deze lauwwarme infusie met een lepeltje honing — een prima vervanger voor industriële zoete drankjes.</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -729,41 +703,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Thé vert — rose, poire</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Groene thee — roos, peer</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>27/05/2027</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="K3" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="L3" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="M3" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>11.5</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -811,7 +783,6 @@
 Moment van consumptie: Overdag</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -839,41 +810,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Infusion épicée — réglisse, anis, fleur de mauve</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Kruideninfusie — zoethout, anijs, kaasjeskruid</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>27/09/2027</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="L4" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>11.5</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -923,7 +892,6 @@
 Zoethout werd al gebruikt door de Egyptische farao's omwille van zijn kalmerende eigenschappen — een eeuwenoude traditie die de moderne smaakpapillen blijft boeien.</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -951,41 +919,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Thé vert BIO — maté, citronnelle</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Groene thee BIO — maté, citroengras</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>15/10/2027</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="L5" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="O5" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>7.7</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -1053,11 +1019,6 @@
 Wist je dat? Citroengras (Cymbopogon) heeft niets met citroen te maken — het is een tropisch gras. Zijn citroenaroma komt van citraal, hetzelfde molecuul als in citroenschil. De natuur heeft hetzelfde parfum twee keer uitgevonden, in twee totaal verschillende planten.</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 7.70 € ≠ prix catalogue 11.50 €</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1085,41 +1046,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Thé vert — goji, açaï, sureau</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Groene thee — goji, açaí, vlierbes</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>03/09/2027</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="L6" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>11.5</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
@@ -1167,7 +1126,6 @@
 Drinkmoment: Overdag</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1195,41 +1153,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Thé vert — fraise, rose, canneberge</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Groene thee — aardbei, roos, veenbes</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>01/04/2028</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="L7" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="O7" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>11.5</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1233,6 @@
 Consumptie moment: Overdag</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1305,41 +1260,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Thé vert — bergamote, bleuet</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Groene thee — bergamot, korenbloem</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>01/04/2028</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="L8" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="M8" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="O8" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>11.5</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
@@ -1387,7 +1340,6 @@
 Consumptietijd: Overdag</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1415,41 +1367,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Thé noir — bergamote, citron, orange</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee — bergamot, citroen, sinaasappel</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>03/12/2027</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="L9" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>11.5</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
@@ -1519,7 +1469,6 @@
 Wist je dat? De naam "Earl Grey" komt van Charles Grey, 2de Graaf Grey en Brits premier van 1830 tot 1834. Volgens de legende zou het recept hem geschonken zijn door een Chinese mandarijn als dank voor een diplomatieke gunst. Het recept gebruikte bergamotolie om de kalksmaak van het harde water van zijn landgoed in Northumberland te maskeren.</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1547,41 +1496,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Rooibos — poire, datte, raisin, citronnelle</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Rooibos — peer, dadel, rozijn, citroengras</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="I10" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>01/10/2027</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="L10" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="M10" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="O10" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>11.5</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1629,7 +1576,6 @@
 Consumptemoment: Naar keuze</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1657,41 +1603,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Maté — menthe poivrée, citronnelle, orange</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Maté — pepermunt, citroengras, sinaasappel</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="I11" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>01/04/2028</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="L11" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="O11" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>7.7</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1757,11 +1701,6 @@
 Wist je dat? In Argentinië deelt men maté: één recipiënt, één bombilla (metalen rietje), en men geeft het van hand tot hand door. Een maté weigeren die men je aanbiedt, wordt beschouwd als een belediging. Hier zijn we soepeler — maar we hopen dat je de jouwe niet zult weigeren.</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 7.70 € ≠ prix catalogue 11.50 €</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1789,41 +1728,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Thé noir nature — Inde</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee natuur — India</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="I12" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>01/04/2028</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="K12" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="L12" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>6.51</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>11.5</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1808,6 @@
 Consumptie moment: Ochtend</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1899,41 +1835,39 @@
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Thé noir nature BIO — Darjeeling</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee natuur BIO — Darjeeling</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>04/02/2028</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="K13" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="L13" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="M13" s="4" t="n">
         <v>12.26</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>7.8</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="O13" s="4" t="n">
         <v>7.36</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>13</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
@@ -1983,121 +1917,78 @@
 Consumptietijd: Ochtend</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>2 lignes d'inventaire regroupées · DLU : 13/04/2028, 04/02/2028</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>I070</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>15/06/2027</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="6" t="inlineStr"/>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="6" t="inlineStr"/>
-      <c r="T14" s="7" t="inlineStr">
-        <is>
-          <t>Référence inconnue dans Odoo : I0700 (Anti Fatigue) ou I0709 (Parfums d'été) ? À confirmer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>I0728</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>5413393802819</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Jardin gourmand</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Jardin gourmand</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Infusion de plantes — pomme, framboise, millepertuis</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Kruideninfusie — appel, framboos, sint-janskruid</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>13/04/2028</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="K14" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="L14" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="M14" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="O14" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O15" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0728-Jardin-gourmand-Infusion-de-plantes-pomme-framboise-Jardin-gourmand-Teatower.jpg?v=1762729376</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-plantes-pomme-framboise-jardin-gourmand-teatower</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Jardin gourmand
 Il y a des matins où l'on se réveille avec l'envie de croquer dans un fruit frais, encore perlé de rosée. Cette infusion-là, c'est exactement ce moment capturé dans votre tasse. Comme si vous veniez de cueillir pommes et framboises dans un jardin secret, celui où les plantes se mélangent aux parfums sucrés de l'enfance.
@@ -2116,7 +2007,7 @@
 Les granulés de framboise fondent lentement dans l'eau chaude, libérant leur couleur et leur saveur authentique — un petit secret gourmand qui fait toute la différence.</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Jardin gourmand
 Er zijn ochtenden waarop je wakker wordt met zin om in een vers fruit te bijten, nog parelend van dauw. Deze infusie vangt precies dat moment in je kopje. Alsof je zojuist appels en frambozen hebt geplukt in een geheime tuin, waar planten zich vermengen met de zoete geuren van de jeugd.
@@ -2135,85 +2026,78 @@
 De frambozenkorrels smelten langzaam in het warme water en geven hun kleur en authentieke smaak vrij — een klein verwennend geheimpje dat het verschil maakt.</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>2 lignes d'inventaire regroupées</t>
-        </is>
-      </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>I0737</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>5413393802857</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Plaisir caramel</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Karamelgenot</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Rooibos — caramel</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Rooibos — karamel</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="I15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>24/08/2027</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="K15" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="L15" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="O15" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O16" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0737-Plaisir-caramel-Rooibos-caramel-Plaisir-caramel-Teatower.jpg?v=1762729390</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/rooibos-caramel-plaisir-caramel-teatower</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>Plaisir caramel
 Plaisir caramel est une infusion de rooibos délicieusement gourmande aux notes suaves et réconfortantes de caramel. Naturellement sans théine, elle offre une tasse douce et onctueuse, parfaite pour une pause cocooning à savourer à tout moment de la journée.
@@ -2232,7 +2116,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>Plaisir caramel
 Plaisir caramel is a rooibos infusion deliciously indulgent with sweet and comforting caramel notes. Naturally caffeine-free, it offers a sweet and creamy cup, perfect for a cosy break to savour at any time of day.
@@ -2251,81 +2135,78 @@
 Time to enjoy: Anytime</t>
         </is>
       </c>
-      <c r="T16" s="3" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>I0742</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>5413393803069</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Ange Gardien</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Beschermengel</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Oolong — fraise, goji</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Oolong — aardbei, goji</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="I16" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>27/05/2027</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="K16" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="L16" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="M16" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="N16" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="O16" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O17" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0742-Ange-Gardien-Oolong-mangue-fraise-Ange-Gardien-Teatower.jpg?v=1762729392</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/oolong-mangue-fraise-ange-gardien-teatower</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Ange Gardien
 Le thé oolong parfumé Ange Gardien marie délicatement Goji – Fraise pour une tasse fruitée, douce et réconfortante. Un oolong faible en théine, parfait pour une pause gourmande à tout moment de la journée.
@@ -2343,7 +2224,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Ange Gardien
 De geparfumeerde oolong thee Ange Gardien combineert delicaat Goji – Aardbei voor een fruitige, zachte en troostende kop thee. Een oolong arm aan cafeïne, perfect voor een lekkere pauze op elk moment van de dag.
@@ -2361,81 +2242,78 @@
 Consumptietijdstip: Naar keuze</t>
         </is>
       </c>
-      <c r="T17" s="3" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>I0772</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>5413393802987</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Thé noir parfumé ananas rose fleurs de bleuet- Black Bloom (ancien nom Black Mango)</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Black Bloom (oude naam Black Mango)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Thé noir — ananas, rose, bleuet</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee — ananas, roos, korenbloem</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="I17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>03/09/2027</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="K17" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="L17" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="M17" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="N17" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="O17" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O18" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0772-Black-Mango-The-noir-aromatise-mangue-Black-Mango-Teatower.jpg?v=1762729406</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-noir-aromatise-mangue-black-mango-teatower</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>Black bloom
 Black bloom est un thé noir parfumé aux notes fruitées et florales d’ananas, de rose et de fleurs de bleuet. Élégant et délicat, il offre une infusion harmonieuse où la douceur exotique de l’ananas se mêle à la finesse florale pour une tasse raffinée à savourer en journée.
@@ -2453,7 +2331,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>Black bloom
 Black bloom is een gearomatiseerde zwarte thee met fruitige en florale toetsen van ananas, roos en korenbloembloemen. Elegant en delicaat, biedt het een harmonieuze infusie waarin de exotische zoetheid van de ananas zich vermengt met de florale finesse voor een verfijnde kop om overdag te genieten.
@@ -2471,81 +2349,78 @@
 Consumptietijd: Overdag</t>
         </is>
       </c>
-      <c r="T18" s="3" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>I0775</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>5413393803519</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Promenade à Venise</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Promenade à Venise</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Thé noir — framboise, canneberge, amande, orange</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee — framboos, veenbes, amandel, sinaasappel</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="I18" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>14/01/2028</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="K18" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="L18" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="M18" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="N18" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="O18" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O19" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0775-Promenade-a-venise-The-noir-aromatise-framboise-canneberge-Promenade-a-Venise-Teatower.jpg?v=1762729412</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-noir-aromatise-framboise-canneberge-promenade-a-venise-teatower</t>
         </is>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>Promenade à Venise
 Promenade à Venise est un thé noir parfumé aux accents fruités et gourmands de framboise, de canneberge, d’amande et d’orange. Élégant et harmonieux, il évoque une balade raffinée entre douceur fruitée et notes délicatement épicées, pour une tasse chaleureuse à savourer en journée.
@@ -2566,7 +2441,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>Promenade à Venise
 Promenade à Venise is een gearomatiseerde zwarte thee met fruitige en verwennende accenten van framboos, veenbes, amandel en sinaasappel. Elegant en harmonieus, roept het een verfijnde wandeling op tussen fruitige zoetheid en delicaat gekruide toetsen, voor een warme kop thee om overdag van te genieten.
@@ -2587,81 +2462,78 @@
 Drinkmoment: Overdag</t>
         </is>
       </c>
-      <c r="T19" s="3" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>I0778</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>5413393803014</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Spéculoos &amp; Cie</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Spéculoos &amp; Cie</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Thé noir — spéculoos : cardamome, amande, cannelle</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee — speculaas: kardemom, amandel, kaneel</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="I19" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>01/10/2027</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="K19" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="L19" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="M19" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="N19" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="O19" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O20" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0778-Speculoos-Cie-The-noir-aromatise-cannelle-speculoos-Speculoos-Cie-Teatower.jpg?v=1762729414</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-noir-aromatise-cannelle-speculoos-speculoos-cie-teatower</t>
         </is>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>Spéculoos &amp; Cie
 Spéculoos &amp; Cie est un thé noir parfumé aux notes chaleureuses et épicées de cardamome, d’amandes et de cannelle. Gourmand et réconfortant, il évoque l’univers des douceurs d’hiver et offre une infusion généreuse et enveloppante, idéale pour une pause plaisir en journée.
@@ -2680,7 +2552,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>Spéculoos &amp; Cie
 Spéculoos &amp; Cie is een gearomatiseerde zwarte thee met warme en kruidige toetsen van kardemom, amandelen en kaneel. Verwennend en troostend, het roept de wereld van winterse lekkernijen op en biedt een royale en omhullende infusie, ideaal voor een genietmoment overdag.
@@ -2699,81 +2571,78 @@
 Consumptie moment: Overdag</t>
         </is>
       </c>
-      <c r="T20" s="3" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>I0813</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>5413393803380</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Thé du désert</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thé du désert</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Thé vert — menthe</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Groene thee — munt</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="I20" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>16/12/2027</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="K20" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="L20" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="M20" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="N20" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="O20" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O21" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0813-The-du-desert-The-vert-aromatise-menthe-The-du-desert-Teatower.jpg?v=1762729441</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-aromatise-menthe-the-du-desert-teatower</t>
         </is>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>Thé du désert
 Le Thé du désert est un thé vert parfumé à la menthe,
@@ -2796,7 +2665,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Thé du désert
 De Thé du désert is een groene thee gearomatiseerd met munt,
@@ -2819,81 +2688,78 @@
 Consumentiemoment: Overdag</t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>I0816</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>5413393803571</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Vitalité BIO</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Vitalité BIO</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Thé vert BIO — orange, cannelle, cardamome</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Groene thee BIO — sinaasappel, kaneel, kardemom</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="I21" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>01/08/2027</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="K21" s="4" t="n">
         <v>13.5</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="L21" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="M21" s="4" t="n">
         <v>12.74</v>
       </c>
-      <c r="M22" s="4" t="n">
+      <c r="N21" s="4" t="n">
         <v>8.1</v>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="O21" s="4" t="n">
         <v>7.64</v>
       </c>
-      <c r="O22" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0816-Vitalite-BIO-The-vert-aromatise-orange-cannelle-Vitalite-BIO-Teatower.jpg?v=1762729445</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-aromatise-orange-cannelle-vitalite-bio-teatower</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>Vitalité – BIO
 Un chai sans le lait. Un thé vert avec l’âme d’un marché aux épices. Vitalité, c’est la tasse qui réchauffe de l’intérieur — même quand il fait 25° dehors.
@@ -2921,7 +2787,7 @@
 Le saviez-vous ? La cardamome est surnommée “la reine des épices” en Inde. C’est la troisième épice la plus chère au monde après le safran et la vanille. Quelques graines suffisent à transformer une tasse ordinaire en expérience aromatique.</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>Vitalité – BIO
 Een chai zonder melk. Een groene thee met de ziel van een kruidenmarkt. Vitalité, dat is de kop thee die je van binnenuit opwarmt — zelfs wanneer het buiten 25° is.
@@ -2949,85 +2815,78 @@
 Wist je dat? Kardemom wordt in India "de koningin van de kruiden" genoemd. Het is het op twee na duurste kruid ter wereld, na saffraan en vanille. Een paar zaadjes volstaan om een gewone kop thee om te toveren tot een aromatische belevenis.</t>
         </is>
       </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 13.00 € ≠ prix catalogue 13.50 €</t>
-        </is>
-      </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>I0821</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>5413393808477</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Matin des îles (ancien nom Poupée russe)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Matin des îles (oude naam Poupée russe)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Thé noir — ananas, mangue, papaye</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee — ananas, mango, papaja</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="I22" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>13/04/2028</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="K22" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="L22" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="M22" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="N22" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="O22" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O23" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0821-Poupee-russe-The-noir-aromatise-ananas-citron-Poupee-russe-Teatower.jpg?v=1762729454</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-noir-aromatise-ananas-citron-poupee-russe-teatower</t>
         </is>
       </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>Matin des îles
 7h du matin. Dehors il pleut (on est en Belgique). Mais dans votre tasse, c’est les Caraïbes. L’ananas explose, la mangue enveloppe, et le thé noir vous réveille avec cette énergie des matins où tout est possible.
@@ -3054,7 +2913,7 @@
 Le saviez-vous ? L’ananas met 2 à 3 ans à pousser. Un seul fruit par plante, une seule récolte. Quand vous buvez ce thé, vous avez dans votre tasse le résultat de 3 ans de patience tropicale.</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>Matin des îles
 7 uur 's ochtends. Buiten regent het (we zijn in België). Maar in je kopje is het de Caraïben. De ananas explodeert, de mango omhult, en de zwarte thee wekt je met die energie van ochtenden waar alles mogelijk is.
@@ -3081,81 +2940,78 @@
 Wist je dat? Een ananas heeft 2 tot 3 jaar nodig om te groeien. Eén vrucht per plant, één oogst. Wanneer je deze thee drinkt, heb je in je kopje het resultaat van 3 jaar tropisch geduld.</t>
         </is>
       </c>
-      <c r="T23" s="3" t="inlineStr"/>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>I0822</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>5413393808484</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Sous les cocotiers</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sous les cocotiers</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — coco, melon</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — kokos, meloen</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="I23" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>08/01/2028</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="K23" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="L23" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="M23" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="N23" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="O23" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O24" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0822-Sous-les-cocotiers-Infusion-de-fruits-coco-melon-Sous-les-cocotiers-Teatower.jpg?v=1762729457</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-coco-melon-sous-les-cocotiers-teatower</t>
         </is>
       </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>Sous les cocotiers
 Premier jour de vacances. Vous êtes allongé sur le sable chaud, une brise légère apporte un parfum de coco et de melon. Quelqu’un vous tend un verre fraîchement pressé. Vous fermez les yeux et souriez. Sous les cocotiers, c’est ce moment-là — en infusion.
@@ -3184,7 +3040,7 @@
 Le saviez-vous ? Le cocotier est appelé “l’arbre de vie” car chaque partie est utilisable : l’eau, le lait, la chair, l’huile, la coque (charbon), les feuilles (toitures), et même les fibres (cordage). Un seul cocotier peut produire pendant 80 ans. C’est la nature à son meilleur.</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>Onder de Kokospalmen
 Eerste vakantiedag. Je ligt languit op het warme zand, een lichte bries brengt de geur van kokos en meloen. Iemand reikt je een vers geperst glas aan. Je sluit je ogen en glimlacht. Onder de Kokospalmen, dat is dit moment — als infusie.
@@ -3213,85 +3069,78 @@
 Wist je dat? De kokospalm wordt "de boom des levens" genoemd omdat elk onderdeel bruikbaar is: het water, de melk, het vruchtvlees, de olie, de dop (houtskool), de bladeren (dakbedekkingen), en zelfs de vezels (touw). Eén kokospalm kan 80 jaar lang produceren. Dat is de natuur op zijn best.</t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t>2 lignes d'inventaire regroupées</t>
-        </is>
-      </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>I0826</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>5413393808620</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Duo Tropical BIO (ancien nom Pinacolada BIO)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Duo Tropical BIO (oude naam Pinacolada BIO)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits BIO — coco, ananas</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie BIO — kokos, ananas</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="I24" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>14/01/2028</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="K24" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="L24" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="M24" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="N24" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="O24" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O25" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0826-Pinacolada-Infusion-de-fruits-coco-ananas-Pinacolada-Teatower.jpg?v=1762729462</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-coco-ananas-pinacolada-teatower</t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Duo Tropical
 Fermer les yeux et sentir le sable chaud sous ses pieds. Écouter le bruit des vagues qui se brisent doucement sur la plage. Cette tasse, c'est votre billet d'évasion vers les îles — sans quitter votre cuisine. Un voyage tropical qui commence dès la première gorgée.
@@ -3311,7 +3160,7 @@
 Astuce gourmande : ajoutez une rondelle de citron vert pour un twist cocktail encore plus exotique.</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>Duo Tropical
 De ogen sluiten en het warme zand onder je voeten voelen. Luisteren naar het geluid van golven die zachtjes op het strand breken. Deze kop is jouw vrijgeleide naar de eilanden — zonder je keuken te verlaten. Een tropische reis die begint vanaf de eerste teug.
@@ -3331,81 +3180,78 @@
 Lekkere tip: voeg een schijfje limoen toe voor een nog exotischere cocktailtwist.</t>
         </is>
       </c>
-      <c r="T25" s="3" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>I0829</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>5413393809085</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Tropical Sun</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tropical Sun</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Thé vert &amp; noir — ananas, orange, citron</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Groene &amp; zwarte thee — ananas, sinaasappel, citroen</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="I25" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>01/04/2028</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="K25" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K26" s="5" t="n">
+      <c r="L25" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="M25" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="N25" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="O25" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O26" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0829-Tropical-Sun-The-vert-melon-mangue-ananas-Tropical-Sun-Teatower.jpg?v=1762729468</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-melon-mangue-ananas-tropical-sun-teatower</t>
         </is>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>Tropical Sun
 Tropical Sun est un thé vert parfumé ensoleillé et rafraîchissant, qui associe des notes exotiques d’ananas à la vivacité de l’orange et du citron. Une infusion lumineuse, parfaite pour une pause fruitée et énergisante.
@@ -3423,7 +3269,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>Tropical Sun
 Tropical Sun is een zonnige en verfrissende geparfumeerde groene thee, die exotische ananastoetsen combineert met de levendigheid van sinaasappel en citroen. Een lichtgevende infusie, perfect voor een fruitige en energiegevende pauze.
@@ -3441,81 +3287,78 @@
 Consumptietijdstip: Overdag</t>
         </is>
       </c>
-      <c r="T26" s="3" t="inlineStr"/>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>I0834</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>5413393811811</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Nuage Coco</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Nuage Coco</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Maté — coco</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Maté — kokos</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="I26" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>01/10/2027</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="K26" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="L26" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="M26" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="N26" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="O26" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O27" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0834-Nuage-Coco-Mate-coco-Nuage-Coco-Teatower.jpg?v=1762729472</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/mate-coco-nuage-coco-teatower</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>Nuage Coco
 Nuage Coco est un maté gourmand mariant la puissance végétale du maté à la douceur exotique de la noix de coco. Réconfortante et enveloppante, cette création offre une infusion ronde et chaleureuse, idéale pour un réveil en douceur tout en énergie.
@@ -3534,7 +3377,7 @@
 Moment de consommation : Matin</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>Nuage Coco
 Nuage Coco is een verwennende maté die de plantaardige kracht van maté verenigt met de exotische zachtheid van kokosnoot. Troostend en omhullend, deze creatie biedt een ronde en warme infusie, ideaal voor een zachte opwekker vol energie.
@@ -3553,81 +3396,78 @@
 Consumptie moment: Ochtend</t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr"/>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>I0837</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>5413393812009</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Eclat de Pistache (ancien nom Vert Pistache)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Eclat de Pistache (oude naam Vert Pistache)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Thé vert — pistache, pomme, canneberge</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Groene thee — pistache, appel, veenbes</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="I27" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>04/02/2028</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="K27" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="L27" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="M27" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="N27" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="O27" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O28" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0837-Vert-Pistache-The-vert-aromatise-pistache-Vert-Pistache-Teatower.jpg?v=1762729480</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-aromatise-pistache-vert-pistache-teatower</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>Éclat de Pistache
 Imaginez un macaron pistache fondu dans une tasse de thé vert. Maintenant arrêtez d’imaginer — c’est exactement ça.
@@ -3655,7 +3495,7 @@
 Le saviez-vous ? La pistache n’est pas une noix — c’est le fruit d’un arbre de la famille des anacardiacées (comme la mangue et l’anacarde). Les meilleurs pistachiers mettent 15 à 20 ans avant de produire leur première récolte. La patience a un goût — c’est celui-ci.</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>Éclat de Pistache
 Stel je voor: een pistache macaron die smelt in een kopje groene thee. Stop met je voorstellen — dit is het precies.
@@ -3683,85 +3523,78 @@
 Wist je dat? Pistache is geen noot — het is de vrucht van een boom uit de cashewfamilie (zoals mango en cashew). De beste pistachebomen hebben 15 tot 20 jaar nodig voordat ze hun eerste oogst produceren. Geduld heeft een smaak — en dit is die smaak.</t>
         </is>
       </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t>2 lignes d'inventaire regroupées</t>
-        </is>
-      </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>I0843</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>5413393812184</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Milky Oolong BIO</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Milky Oolong BIO</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>Oolong BIO — lacté, vanillé</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Oolong BIO — melkachtig, vanille</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="I28" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>15/01/2027</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="K28" s="4" t="n">
         <v>13.85</v>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="L28" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="M28" s="4" t="n">
         <v>13.07</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="N28" s="4" t="n">
         <v>8.31</v>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="O28" s="4" t="n">
         <v>7.84</v>
       </c>
-      <c r="O29" s="4" t="n">
-        <v>9.69</v>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0843-Milky-Oolong-BIO-Oolong-vanille-lait-Milky-Oolong-BIO-Teatower.jpg?v=1762729492</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/oolong-vanille-lait-milky-oolong-bio-teatower</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>Milky Oolong - BIO
 Le Milky Oolong - BIO est un oolong parfumé biologique reconnu pour sa douceur exceptionnelle et ses notes délicatement lactées et vanillées. Sa tasse onctueuse et soyeuse offre une expérience gourmande et réconfortante, idéale pour une pause élégante et apaisante, à savourer à tout moment de la journée.
@@ -3780,7 +3613,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>Milky Oolong - BIO
 De Milky Oolong - BIO is een biologische geparfumeerde oolong die bekend staat om zijn uitzonderlijke zachtheid en delicate romige vanillenoten. Deze fluweelzachte en romige thee biedt een verwennende en troostrijke ervaring, ideaal voor een elegante en rustgevende pauze op elk moment van de dag.
@@ -3799,85 +3632,78 @@
 Wanneer drinken: Naar keuze</t>
         </is>
       </c>
-      <c r="T29" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 9.69 € ≠ prix catalogue 13.85 €</t>
-        </is>
-      </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>I0847</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>5413393812276</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Pastèque Fraîcheur (ancien nom Couleur Mojito)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Watermeloen Frisheid</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — pastèque, menthe, sureau</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — watermeloen, munt, vlierbes</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>04/02/2028</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="K29" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="L29" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="M29" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="O29" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O30" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0847-Couleur-Mojito-Infusion-de-fruits-pasteque-menthe-Couleur-Mojito-Teatower.jpg?v=1762729500</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-pasteque-menthe-couleur-mojito-teatower</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>Pastèque fraîcheur
 C'est l'heure de la sieste. Dehors, l'été pèse lourd. Vous ouvrez le frigo et sortez une pastèque bien fraîche — ce parfum sucré qui embaume la cuisine, ce bruit sourd du couteau qui tranche... Voilà exactement ce que cette infusion capture dans votre tasse. Une tranche d'été, à boire.
@@ -3896,7 +3722,7 @@
 Laissez refroidir quelques heures au frigo avec des glaçons — vous obtiendrez un thé glacé maison qui rivalise avec les plus belles limonades d'été.</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>```html
 Pastèque fraîcheur
@@ -3917,81 +3743,78 @@
 ```</t>
         </is>
       </c>
-      <c r="T30" s="3" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>I0848</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>5413393812306</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Ginger Cool BIO</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Ginger Cool BIO</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Thé vert BIO — gingembre, citron</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Groene thee BIO — gember, citroen</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="I30" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>22/02/2028</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="K30" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K31" s="5" t="n">
+      <c r="L30" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="M30" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="N30" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="O30" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O31" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0848-Ginger-Cool-BIO-The-vert-gingembre-citron-Ginger-Cool-BIO-Teatower.jpg?v=1762729503</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-gingembre-citron-ginger-cool-bio-teatower</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>Ginger Cool – BIO
 Vos jambes crient après une course. Votre gorge gratte au premier froid. Votre digestion fait des siennes. Trois problèmes, une réponse : gingembre. Et celui-ci est le meilleur qu’on ait trouvé.
@@ -4023,7 +3846,7 @@
 Le saviez-vous ? Le gingembre est utilisé comme remède en médecine traditionnelle chinoise et ayurvédique depuis plus de 5000 ans. Confucius en consommait à chaque repas. Si c’était assez bon pour Confucius…</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>Ginger Cool – BIO
 Uw benen schreeuwen het uit na een loopsessie. Uw keel krast bij de eerste kou. Uw spijsvertering speelt op. Drie problemen, één antwoord: gember. En dit is de beste die we hebben gevonden.
@@ -4055,81 +3878,78 @@
 Wist je dat? Gember wordt al meer dan 5000 jaar gebruikt als geneesmiddel in de traditionele Chinese en ayurvedische geneeskunde. Confucius consumeerde het bij elke maaltijd. Als het goed genoeg was voor Confucius…</t>
         </is>
       </c>
-      <c r="T31" s="3" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>I0866</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>5413393813051</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Escale à Cassis</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Escale à Cassis</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Thé noir — cassis</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee — zwarte bes</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="I31" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>13/04/2028</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="K31" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="L31" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M32" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="O31" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O32" s="4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0866-Escale-a-Cassis-The-noir-aromatise-cassis-Escale-a-Cassis-Teatower.jpg?v=1762729525</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-noir-aromatise-cassis-escale-a-cassis-teatower</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>Escale à Cassis
 Escale à Cassis est un thé noir parfumé intensément fruité, mettant à l’honneur la richesse aromatique du cassis. Franc et élégant, il offre une infusion gourmande et légèrement acidulée, idéale pour une pause vivifiante au cours de la journée.
@@ -4147,7 +3967,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>Escale à Cassis
 Escale à Cassis is een intens fruitige gearomatiseerde zwarte thee die de aromatische rijkdom van zwarte bessen in de kijker zet. Frank en elegant, biedt hij een lekkere en licht zure infusie, ideaal voor een verkwikkende pauze tijdens de dag.
@@ -4165,85 +3985,78 @@
 Moment van consumptie: Overdag</t>
         </is>
       </c>
-      <c r="T32" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 7.70 € ≠ prix catalogue 11.50 €</t>
-        </is>
-      </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>I0875</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>5413393813143</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Evasion Ambrée</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Evasion Ambrée</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>Rooibos — orange, cassis, cannelle</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Rooibos — sinaasappel, zwarte bes, kaneel</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="I32" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>25/04/2028</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="K32" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="L32" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="M32" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M33" s="4" t="n">
+      <c r="N32" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="O32" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O33" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0875-Souvenir-de-La-havane-Rooibos-rhum-Souvenir-de-La-Havane-Teatower.jpg?v=1762729544</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/rooibos-rhum-souvenir-de-la-havane-teatower</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>Evasion ambrée
 Évasion Ambrée, la nouvelle identité de notre rooibos Souvenir de la Havane. Sans changer sa recette, ce nouveau nom met parfaitement en avant son univers chaleureux, épicé et délicatement fruité, inspiré des ambiances solaires et ambrées.
@@ -4262,7 +4075,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>Evasion ambrée
 Évasion Ambrée, de nieuwe identiteit van onze rooibos Souvenir de la Havane. Zonder de receptuur te wijzigen, brengt deze nieuwe naam perfect zijn warme, gekruide en delicaat fruitige universum naar voren, geïnspireerd door zonrijke en amberen sferen.
@@ -4281,85 +4094,78 @@
 Consumptietijd: Naar keuze</t>
         </is>
       </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t>2 lignes d'inventaire regroupées</t>
-        </is>
-      </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>I0879</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>5413393813471</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Amazônia</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Amazônia</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Maté — mangue, clémentine, banane</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Maté — mango, clementine, banaan</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="I33" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>06/11/2027</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="K33" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K34" s="5" t="n">
+      <c r="L33" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="M33" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M34" s="4" t="n">
+      <c r="N33" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="O33" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O34" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0879-Amazonia-Mate-mangue-Amazonia-Teatower.jpg?v=1762729551</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/mate-mangue-amazonia-teatower</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>Amazônia
 Amazônia est un maté aux saveurs exotiques et ensoleillées de mangue, de clémentine et de banane. Tonique et fruité, ce mélange vibrant offre une infusion intensément aromatique, idéale pour faire le plein d’énergie et commencer la journée avec vitalité.
@@ -4381,7 +4187,7 @@
 → Lire le guide complet : rituel calebasse étape par étape</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>Amazônia
 Amazônia is een maté met exotische en zonnige smaken van mango, clementine en banaan. Tonisch en fruitig, biedt dit levendige mengsel een intens aromatische infusie — ideaal om nieuwe energie op te doen en de dag vol vitaliteit te beginnen.
@@ -4403,81 +4209,78 @@
 → Lees de volledige handleiding: het kalebas-ritueel stap voor stap</t>
         </is>
       </c>
-      <c r="T34" s="3" t="inlineStr"/>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>I0885</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>5413393814140</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Cococabana</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Cococabana</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>Thé vert — coco, ananas</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Groene thee — kokos, ananas</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="I34" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>15/06/2027</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="K34" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="L34" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="M34" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="N34" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="O34" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O35" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0885-Cococabana-The-vert-coco-Cococabana-Teatower.jpg?v=1762729561</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-coco-cococabana-teatower</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>Cococabana
 Cococabana est un thé vert parfumé exotique et ensoleillé, qui marie la fraîcheur végétale du thé vert Sencha à la douceur gourmande de la noix de coco et aux notes fruitées de l’ananas. Une invitation à l’évasion, idéale pour une pause dépaysante.
@@ -4495,7 +4298,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>Cococabana
 Cococabana is een exotische en zonnige gearomatiseerde groene thee, die de plantaardige frisheid van Sencha groene thee combineert met de verwennende zoetheid van kokos en de fruitige toetsen van ananas. Een uitnodiging tot ontsnapping, ideaal voor een ontspannende pauze vol exotiek.
@@ -4513,81 +4316,78 @@
 Drinkmoment: Overdag</t>
         </is>
       </c>
-      <c r="T35" s="3" t="inlineStr"/>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>I0890</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>5413393814256</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Mango Fresh (ancien nom Aie Caramba)</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mango Fresh (oude naam Aie Caramba)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Thé vert — ananas, mangue, menthe</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Groene thee — ananas, mango, munt</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="I35" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>04/02/2028</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="K35" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="L35" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="M35" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M36" s="4" t="n">
+      <c r="N35" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="O35" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O36" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0890-Aie-caramba-The-vert-aromatise-cactus-mangue-Aie-Caramba-Teatower.jpg?v=1762729573</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-aromatise-cactus-mangue-aie-caramba-teatower</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>Mango Fresh
 Mango Fresh, la nouvelle identité de notre thé vert Aie Caramba. Cette nouvelle appellation met en valeur son caractère exotique, frais et intensément fruité, tout en conservant la même recette équilibrée et ensoleillée.
@@ -4606,7 +4406,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>Mango Fresh
 Mango Fresh, de nieuwe identiteit van onze groene thee Aie Caramba. Deze nieuwe benaming benadrukt het exotische, frisse en intens fruitige karakter, terwijl hetzelfde evenwichtige en zonnige recept behouden blijft.
@@ -4625,81 +4425,78 @@
 Consumptietijd: Overdag</t>
         </is>
       </c>
-      <c r="T36" s="3" t="inlineStr"/>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>I0897</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>5413393815017</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Sicile Sanguine BIO</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sicile Sanguine BIO</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>Pu erh BIO — orange sanguine, citronnelle, hibiscus</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Pu-erh BIO — bloedsinaasappel, citroengras, hibiscus</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>13/04/2028</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="K36" s="4" t="n">
         <v>13.5</v>
       </c>
-      <c r="K37" s="5" t="n">
+      <c r="L36" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="M36" s="4" t="n">
         <v>12.74</v>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="N36" s="4" t="n">
         <v>8.1</v>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="O36" s="4" t="n">
         <v>7.64</v>
       </c>
-      <c r="O37" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0897-Sicile-Sanguine-BIO-Pu-erh-orange-sanguine-Sicile-Sanguine-BIO-Teatower.jpg?v=1762729583</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/pu-erh-orange-sanguine-sicile-sanguine-bio-teatower</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>Sicile Sanguine - BIO
 Sicile Sanguine - BIO est un pu-erh parfumé biologique aux notes ensoleillées d’orange sanguine, de citronnelle et d’hibiscus. Cette infusion au caractère fruité et légèrement acidulé évoque la Méditerranée et offre une tasse vivifiante, parfaite à tout moment de la journée.
@@ -4718,7 +4515,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>Sicile Sanguine - BIO
 Sicile Sanguine - BIO is een biologische geparfumeerde pu-erh met zonnige noten van bloedsinaasappel, citroengras en hibiscus. Deze infusie met een fruitig en licht zurig karakter roept de Middellandse Zee op en biedt een verkwikkende kop thee, perfect op elk moment van de dag.
@@ -4737,85 +4534,78 @@
 Consumptie moment: Naar keuze</t>
         </is>
       </c>
-      <c r="T37" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 13.00 € ≠ prix catalogue 13.50 €</t>
-        </is>
-      </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>I0899</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>5413393815079</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité (ancien nom Mumbai Mango) BIO</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité (vroeger Mumbai Mango) BIO</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits BIO — pomme, orange, fraise, mangue</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie BIO — appel, sinaasappel, aardbei, mango</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="I37" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>01/10/2027</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="K37" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K38" s="5" t="n">
+      <c r="L37" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="M37" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M38" s="4" t="n">
+      <c r="N37" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="O37" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O38" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0899-Mumbai-Mango-BIO-Infusion-de-fruits-mangue-Mumbai-Mango-BIO-Teatower.jpg?v=1762729586</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-mangue-mumbai-mango-bio-teatower</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité
 C'est dimanche matin, la cuisine sent bon les crêpes. Sur la table, les pots de confiture s'alignent comme des promesses colorées — fraise de Wépion, orange amère, compote de pommes du verger. Vous respirez cette symphonie fruitée et souriez. Dans votre tasse, Festival Fruité raconte exactement cette histoire : l'innocence des matins sucrés, la générosité des fruits qui s'entremêlent.
@@ -4835,7 +4625,7 @@
 Astuce : Préparez-la glacée avec une rondelle d'orange fraîche — vos invités penseront à un cocktail sans alcool sophistiqué.</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité
 Het is zondagochtend, de keuken ruikt naar versgebakken pannenkoeken. Op tafel staan de jampotten op een rij als kleurrijke beloftes — Wépion-aardbeien, bittere sinaasappel, appelcompote uit de boomgaard. Je ademt deze fruitige symfonie in en glimlacht. In je kopje vertelt Festival Fruité precies dit verhaal: de onschuld van zoete ochtenden, de vrijgevigheid van vruchten die elkaar omarmen.
@@ -4855,81 +4645,78 @@
 Tip: Bereid hem ijskoud met een schijfje verse sinaasappel — je gasten zullen denken aan een verfijnde alcoholvrije cocktail.</t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr"/>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>I0900</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>5413393815109</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Bora Bora BIO</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Bora Bora BIO</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>20 infusettes</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>Thé noir BIO — pêche, ananas, citronnelle</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee BIO — perzik, ananas, citroengras</t>
         </is>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="I38" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>25/04/2028</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="K38" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="K39" s="5" t="n">
+      <c r="L38" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="M38" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="M39" s="4" t="n">
+      <c r="N38" s="4" t="n">
         <v>6.9</v>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="O38" s="4" t="n">
         <v>6.51</v>
       </c>
-      <c r="O39" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0900-Bora-Bora-BIO-The-noir-aromatise-passion-Bora-Bora-BIO-Teatower_4f2e9195-322a-4284-a012-885b550ea23f.jpg?v=1762729589</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-noir-aromatise-passion-bora-bora-bio-teatower</t>
         </is>
       </c>
-      <c r="R39" s="2" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>Bora Bora - BIO
 Bora Bora - BIO est un thé noir parfumé biologique aux saveurs exotiques et ensoleillées de pêche, de citronnelle et d’ananas. Évocateur d’évasion et de douceur tropicale, il offre une infusion fruitée et rafraîchissante, idéale pour une dégustation en journée.
@@ -4950,7 +4737,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>Bora Bora - BIO
 Bora Bora - BIO is een biologische gearomatiseerde zwarte thee met exotische en zonnige smaken van perzik, citroengras en ananas. Deze thee roept beelden op van ontsnapping en tropische zachtheid en biedt een fruitige en verfrissende infusie, ideaal voor overdag.
@@ -4971,85 +4758,78 @@
 Consumptie moment: Overdag</t>
         </is>
       </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t>2 lignes d'inventaire regroupées</t>
-        </is>
-      </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>V0483</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>5413393801805</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Green Zest BIO</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Green Zest BIO</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Thé vert BIO — maté, citronnelle</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>Groene thee BIO — maté, citroengras</t>
         </is>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="I39" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>06/11/2027</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="K39" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K40" s="5" t="n">
+      <c r="L39" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="M39" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M40" s="4" t="n">
+      <c r="N39" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="O39" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O40" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0483-Green-zest-BIO-The-vert-aromatise-mate-citronnelle-Green-Zest-BIO-Teatower.jpg?v=1762729287</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr">
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-aromatise-mate-citronnelle-green-zest-bio-teatower</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>Green Zest – BIO
 Imaginez un expresso vert. Pas amer. Pas nerveux. Juste cette énergie nette et fraîche qui vous dit “c’est parti” sans crier. Green Zest, c’est le thé vert qui a bu un maté ce matin.
@@ -5077,7 +4857,7 @@
 Le saviez-vous ? La citronnelle (Cymbopogon) n’a rien à voir avec le citron — c’est une graminée tropicale. Son arôme citronné vient du citral, la même molécule que dans le zeste de citron. La nature a inventé le même parfum deux fois, dans deux plantes complètement différentes.</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr">
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>Green Zest – BIO
 Stel je een groene espresso voor. Niet bitter. Niet nerveus. Gewoon die heldere, frisse energie die je zegt "we gaan ervoor" zonder te schreeuwen. Green Zest is de groene thee die vanochtend een maté heeft gedronken.
@@ -5105,85 +4885,78 @@
 Wist je dat? Citroengras (Cymbopogon) heeft niets met citroen te maken — het is een tropisch gras. Zijn citroenaroma komt van citraal, hetzelfde molecuul als in citroenschil. De natuur heeft hetzelfde parfum twee keer uitgevonden, in twee totaal verschillende planten.</t>
         </is>
       </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t>2 lignes d'inventaire regroupées</t>
-        </is>
-      </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>V0601</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>5413393801829</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Acai &amp; goji</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Acai &amp; goji</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>Thé vert — goji, açaï, sureau</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>Groene thee — goji, açaí, vlierbes</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="I40" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>04/02/2028</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="K40" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K41" s="5" t="n">
+      <c r="L40" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="M40" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M41" s="4" t="n">
+      <c r="N40" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="O40" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O41" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0601-Acai-goji-The-vert-aromatise-goji-acai-Acai-goji-Teatower.jpg?v=1762729293</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-aromatise-goji-acai-acai-goji-teatower</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>Acai &amp; Goji
 Acai &amp; Goji est un thé vert parfumé vibrant et fruité, qui associe la fraîcheur végétale du thé vert à la richesse des superfruits. Les notes de goji et d’açaï se mêlent à la douceur du sureau pour une infusion équilibrée, gourmande et pleine d’énergie.
@@ -5201,7 +4974,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>Acai &amp; Goji
 Acai &amp; Goji is een gearomatiseerde groene thee vol levendigheid en fruit, die de plantaardige frisheid van groene thee combineert met de rijkdom van superfruits. De toetsen van goji en açaï vermengen zich met de zachtheid van vlier voor een evenwichtige, verwennende en energieke infusie.
@@ -5219,81 +4992,78 @@
 Drinkmoment: Overdag</t>
         </is>
       </c>
-      <c r="T41" s="3" t="inlineStr"/>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>V0607</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>5413393801881</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Sensualité</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sensualiteit</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>80 g vrac</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Thé vert — fraise, rose, canneberge</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>Groene thee — aardbei, roos, veenbes</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="I41" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>22/02/2028</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="K41" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K42" s="5" t="n">
+      <c r="L41" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="M41" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M42" s="4" t="n">
+      <c r="N41" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="O41" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O42" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0607-Sensualite-The-vert-aromatise-fraise-rose-Sensualite-Teatower.jpg?v=1762729296</t>
         </is>
       </c>
-      <c r="Q42" s="2" t="inlineStr">
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-aromatise-fraise-rose-sensualite-teatower</t>
         </is>
       </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>Sensualité
 Le Sensualité est un thé vert parfumé aux notes délicates et romantiques de fraise et de rose. Subtil et harmonieux, il offre une infusion douce et élégante, idéale pour un moment de plaisir raffiné au cours de la journée.
@@ -5311,7 +5081,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>Sensualité
 De Sensualité is een gearomatiseerde groene thee met delicate en romantische toetsen van aardbei en roos. Subtiel en harmonieus, biedt het een zachte en elegante infusie, ideaal voor een moment van verfijnd genot gedurende de dag.
@@ -5329,81 +5099,78 @@
 Consumptie moment: Overdag</t>
         </is>
       </c>
-      <c r="T42" s="3" t="inlineStr"/>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>V0635</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>5413393802246</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Silhouette</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Silhouette</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>80 g vrac</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Maté — menthe poivrée, citronnelle, orange</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Maté — pepermunt, citroengras, sinaasappel</t>
         </is>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="I42" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>01/04/2028</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="K42" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K43" s="5" t="n">
+      <c r="L42" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="M42" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M43" s="4" t="n">
+      <c r="N42" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="O42" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O43" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0635-Silhouette-Mate-menthe-verveine-Silhouette-Teatower.jpg?v=1762729327</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/mate-menthe-verveine-silhouette-teatower</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>Silhouette
 Le boost du matin sans le crash de 14h. Silhouette, c’est l’énergie du maté sud-américain, la fraîcheur de la menthe belge, et le punch du citron. Un cocktail naturel qui réveille sans brusquer.
@@ -5430,7 +5197,7 @@
 Le saviez-vous ? En Argentine, le maté se partage : un seul récipient, une seule bombilla (paille métallique), et on le passe de main en main. Refuser un maté qu’on vous offre est considéré comme une offense. Ici, on est plus souples — mais on espère que vous ne refuserez pas le vôtre.</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>Silhouette
 De ochtendboost zonder de 14u-crash. Silhouette, dat is de energie van Zuid-Amerikaanse maté, de frisheid van Belgische munt, en de punch van citroen. Een natuurlijke cocktail die wakker maakt zonder te bruuskeren.
@@ -5457,81 +5224,78 @@
 Wist je dat? In Argentinië deelt men maté: één recipiënt, één bombilla (metalen rietje), en men geeft het van hand tot hand door. Een maté weigeren die men je aanbiedt, wordt beschouwd als een belediging. Hier zijn we soepeler — maar we hopen dat je de jouwe niet zult weigeren.</t>
         </is>
       </c>
-      <c r="T43" s="3" t="inlineStr"/>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>V0664</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>5413393802512</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Maté vert du Brésil</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Groene maté uit Brazilië</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Maté vert nature</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Groene maté natuur</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="I43" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>22/02/2028</t>
         </is>
       </c>
-      <c r="J44" s="4" t="n">
+      <c r="K43" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K44" s="5" t="n">
+      <c r="L43" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="M43" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M44" s="4" t="n">
+      <c r="N43" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="O43" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O44" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
+      <c r="P43" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0664-Mate-vert-du-Bresil-Mate-Mate-vert-du-Bresil-Teatower.jpg?v=1762729339</t>
         </is>
       </c>
-      <c r="Q44" s="2" t="inlineStr">
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/mate-mate-vert-du-bresil-teatower</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>Maté vert du Brésil
 Le Maté vert du Brésil est un maté nature au goût franc et végétal, emblématique des traditions sud-américaines. Puissant et tonique, il offre une infusion authentique et stimulante, idéale pour bien démarrer la journée.
@@ -5549,7 +5313,7 @@
 Moment de consommation : Matin</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>Groene Maté uit Brazilië
 De Groene Maté uit Brazilië is een pure maté met een krachtige en plantaardige smaak, emblematisch voor de Zuid-Amerikaanse tradities. Krachtig en tonisch, biedt het een authentieke en stimulerende infusie, ideaal om de dag goed te beginnen.
@@ -5567,81 +5331,78 @@
 Consumptietijdstip: Ochtend</t>
         </is>
       </c>
-      <c r="T44" s="3" t="inlineStr"/>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>V0709</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>5413393800990</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Parfums d'été</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Parfums d'été</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>80 g vrac</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — ananas, pomme, citron, pêche</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — ananas, appel, citroen, perzik</t>
         </is>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="I44" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>04/01/2028</t>
         </is>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="K44" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K45" s="5" t="n">
+      <c r="L44" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="M44" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M45" s="4" t="n">
+      <c r="N44" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="O44" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O45" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0709-Parfums-dete-Infusion-de-fruits-ananas-pomme-Parfums-dete-Teatower.jpg?v=1762729357</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr">
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-ananas-pomme-parfums-dete-teatower</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>Parfums d'été
 C'est juillet, la terrasse sent bon la lavande et les barbecues du quartier. Vous versez l'eau frémissante sur ces morceaux d'ananas dorés et de pomme croquante. Soudain, c'est tout l'été qui monte dans votre tasse — cette acidité joyeuse du citron vert, cette douceur de pêche qui vous ramène aux vacances d'enfance. Même en plein hiver, une gorgée suffit : vous voilà transporté sous le soleil de midi.
@@ -5660,7 +5421,7 @@
 Cette infusion révèle toute sa magie servie glacée avec quelques feuilles de menthe fraîche — l'été n'aura jamais eu meilleur goût.</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>Parfums d'été
 Het is juli, het terras ruikt heerlijk naar lavendel en de barbecues uit de buurt. Je giet het dampende water over deze stukjes gouden ananas en knapperige appel. Plots stijgt de hele zomer op uit je kopje — die vrolijke zuurheid van limoen, die zachte perzikzoetheid die je terugvoert naar de kindervakantie. Ook midden in de winter volstaat één slok: je waant je onder de middagzon.
@@ -5679,81 +5440,78 @@
 Deze infusie toont al zijn magie ijskoud geserveerd met enkele verse muntblaadjes — de zomer heeft nog nooit zo goed gesmaakt.</t>
         </is>
       </c>
-      <c r="T45" s="3" t="inlineStr"/>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>V0710</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>5413393800969</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Dragon nectar (ancien nom mandarine)</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Dragon nectar (oude naam mandarijn)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>80 g vrac</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — mandarine, gingembre, fruit du dragon</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — mandarijn, gember, drakenvrucht</t>
         </is>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="I45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>04/12/2027</t>
         </is>
       </c>
-      <c r="J46" s="4" t="n">
+      <c r="K45" s="4" t="n">
         <v>13.5</v>
       </c>
-      <c r="K46" s="5" t="n">
+      <c r="L45" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L46" s="4" t="n">
+      <c r="M45" s="4" t="n">
         <v>12.74</v>
       </c>
-      <c r="M46" s="4" t="n">
+      <c r="N45" s="4" t="n">
         <v>8.1</v>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="O45" s="4" t="n">
         <v>7.64</v>
       </c>
-      <c r="O46" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0710-Mandarine-Infusion-de-fruits-gingembre-mandarine-Mandarine-Teatower.jpg?v=1762729360</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="inlineStr">
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-gingembre-mandarine-mandarine-teatower</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
+      <c r="R45" s="2" t="inlineStr">
         <is>
           <t>Dragon nectar
 Il était une fois, dans les jardins suspendus d'une île lointaine, un dragon bienveillant qui ne crachait pas le feu, mais un nectar doré aux saveurs d'agrumes. Chaque gorgée raconte cette légende : la mandarine espiègle danse avec le gingembre audacieux, tandis que le fruit du dragon murmure ses secrets de douceur exotique. Une tasse qui transforme votre pause en voyage vers des terres enchantées.
@@ -5772,7 +5530,7 @@
 Astuce : servez-la glacée avec quelques rondelles d'orange fraîche pour un cocktail de fruits naturel et désaltérant.</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr">
         <is>
           <t>Dragon nectar
 Er was eens, in de hangende tuinen van een ver eiland, een welwillende draak die geen vuur spuwde, maar een gouden nectar met citrusaroma's. Elke teug vertelt deze legende: de speelse mandarijn danst met de gedurfde gember, terwijl de drakenfruit zijn geheimen van exotische zoetheid fluistert. Een kopje dat uw pauze transformeert tot een reis naar betoverde landen.
@@ -5791,85 +5549,78 @@
 Tip: serveer gekoeld met enkele schijfjes verse sinaasappel voor een natuurlijke en verfrissende vruchtencocktail.</t>
         </is>
       </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 13.00 € ≠ prix catalogue 13.50 €</t>
-        </is>
-      </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>V0742</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>5413393800358</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Ange Gardien</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Beschermengel</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>Oolong — fraise, goji</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Oolong — aardbei, goji</t>
         </is>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="I46" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>22/02/2028</t>
         </is>
       </c>
-      <c r="J47" s="4" t="n">
+      <c r="K46" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K47" s="5" t="n">
+      <c r="L46" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="M46" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M47" s="4" t="n">
+      <c r="N46" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="O46" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O47" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0742-Ange-Gardien-Oolong-mangue-fraise-Ange-Gardien-Teatower.jpg?v=1762729392</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr">
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/oolong-mangue-fraise-ange-gardien-teatower</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>Ange Gardien
 Le thé oolong parfumé Ange Gardien marie délicatement Goji – Fraise pour une tasse fruitée, douce et réconfortante. Un oolong faible en théine, parfait pour une pause gourmande à tout moment de la journée.
@@ -5887,7 +5638,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>Ange Gardien
 De geparfumeerde oolong thee Ange Gardien combineert delicaat Goji – Aardbei voor een fruitige, zachte en troostende kop thee. Een oolong arm aan cafeïne, perfect voor een lekkere pauze op elk moment van de dag.
@@ -5905,81 +5656,78 @@
 Consumptietijdstip: Naar keuze</t>
         </is>
       </c>
-      <c r="T47" s="3" t="inlineStr"/>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>V0788</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>5413393800624</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Japan Sencha Yamato</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Japan Sencha Yamato</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>50g vrac</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Thé vert nature — Sencha du Japon</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Groene thee natuur — Japanse Sencha</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="I47" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>01/04/2028</t>
         </is>
       </c>
-      <c r="J48" s="4" t="n">
+      <c r="K47" s="4" t="n">
         <v>18.5</v>
       </c>
-      <c r="K48" s="5" t="n">
+      <c r="L47" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L48" s="4" t="n">
+      <c r="M47" s="4" t="n">
         <v>17.45</v>
       </c>
-      <c r="M48" s="4" t="n">
+      <c r="N47" s="4" t="n">
         <v>11.1</v>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="O47" s="4" t="n">
         <v>10.47</v>
       </c>
-      <c r="O48" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0788-Japan-Sencha-Yamato-Finest-quality-The-vert-nature-Japan-Sencha-Yamato-Teatower.jpg?v=1762729417</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="inlineStr">
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-nature-japan-sencha-yamato-teatower</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="R47" s="2" t="inlineStr">
         <is>
           <t>Japan Sencha Yamato – Finest quality
 Le Japan Sencha Yamato – Finest quality est un thé vert d’exception, issu de feuilles de Sencha haut de gamme du Japon. Référence emblématique des thés verts japonais, il séduit par son caractère à la fois végétal, frais et intensément aromatique.
@@ -5997,7 +5745,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr">
+      <c r="S47" s="2" t="inlineStr">
         <is>
           <t>Japan Sencha Yamato – Finest quality
 De Japan Sencha Yamato – Finest quality is een uitzonderlijke groene thee, afkomstig van premium Sencha bladeren uit Japan. Deze emblematische referentie van Japanse groene theeën bekoort door zijn karakter dat tegelijk vegetaal, fris en intens aromatisch is.
@@ -6015,85 +5763,78 @@
 Consumptie moment: Overdag</t>
         </is>
       </c>
-      <c r="T48" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 18.00 € ≠ prix catalogue 18.50 €</t>
-        </is>
-      </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>V0793</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>5413393800341</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Orangipane</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Orangipane</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>Thé vert — orange, amande, fleur d'oranger</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Groene thee — sinaasappel, amandel, oranjebloesem</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="I48" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>18/03/2028</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n">
+      <c r="K48" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K49" s="5" t="n">
+      <c r="L48" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="M48" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M49" s="4" t="n">
+      <c r="N48" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="O48" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O49" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0793-Orangipane-The-vert-orange-amande-Orangipane-Teatower.jpg?v=1762729419</t>
         </is>
       </c>
-      <c r="Q49" s="2" t="inlineStr">
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-orange-amande-orangipane-teatower</t>
         </is>
       </c>
-      <c r="R49" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>Orangipane
 L’Orangipane est un thé vert parfumé gourmand et chaleureux,
@@ -6119,7 +5860,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr">
+      <c r="S48" s="2" t="inlineStr">
         <is>
           <t>Orangipane
 Orangipane is een geparfumeerde groene thee met een verwarmende, verwennende smaak,
@@ -6145,81 +5886,78 @@
 Consumptietijd: Overdag</t>
         </is>
       </c>
-      <c r="T49" s="3" t="inlineStr"/>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>V0822</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>5413393808422</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Sous les cocotiers</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sous les cocotiers</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — coco, melon</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — kokos, meloen</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="I49" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>11/02/2028</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n">
+      <c r="K49" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K50" s="5" t="n">
+      <c r="L49" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L50" s="4" t="n">
+      <c r="M49" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M50" s="4" t="n">
+      <c r="N49" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="O49" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O50" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0822-Sous-les-cocotiers-Infusion-de-fruits-coco-melon-Sous-les-cocotiers-Teatower.jpg?v=1762729457</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="inlineStr">
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-coco-melon-sous-les-cocotiers-teatower</t>
         </is>
       </c>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>Sous les cocotiers
 Premier jour de vacances. Vous êtes allongé sur le sable chaud, une brise légère apporte un parfum de coco et de melon. Quelqu’un vous tend un verre fraîchement pressé. Vous fermez les yeux et souriez. Sous les cocotiers, c’est ce moment-là — en infusion.
@@ -6248,7 +5986,7 @@
 Le saviez-vous ? Le cocotier est appelé “l’arbre de vie” car chaque partie est utilisable : l’eau, le lait, la chair, l’huile, la coque (charbon), les feuilles (toitures), et même les fibres (cordage). Un seul cocotier peut produire pendant 80 ans. C’est la nature à son meilleur.</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr">
+      <c r="S49" s="2" t="inlineStr">
         <is>
           <t>Onder de Kokospalmen
 Eerste vakantiedag. Je ligt languit op het warme zand, een lichte bries brengt de geur van kokos en meloen. Iemand reikt je een vers geperst glas aan. Je sluit je ogen en glimlacht. Onder de Kokospalmen, dat is dit moment — als infusie.
@@ -6277,81 +6015,78 @@
 Wist je dat? De kokospalm wordt "de boom des levens" genoemd omdat elk onderdeel bruikbaar is: het water, de melk, het vruchtvlees, de olie, de dop (houtskool), de bladeren (dakbedekkingen), en zelfs de vezels (touw). Eén kokospalm kan 80 jaar lang produceren. Dat is de natuur op zijn best.</t>
         </is>
       </c>
-      <c r="T50" s="3" t="inlineStr"/>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>V0838</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>5413393812023</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>framboise rose</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>framboos roos</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>Oolong — framboise, rose</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>Oolong — framboos, roos</t>
         </is>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="I50" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>27/12/2027</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n">
+      <c r="K50" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K51" s="5" t="n">
+      <c r="L50" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="M50" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M51" s="4" t="n">
+      <c r="N50" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="O50" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O51" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0838-Oolong-Framboise-Oolong-Framboise-Teatower.jpg?v=1762729482</t>
         </is>
       </c>
-      <c r="Q51" s="2" t="inlineStr">
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/oolong-framboise-teatower</t>
         </is>
       </c>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>Oolong Framboise
 Oolong Framboise est un oolong parfumé délicatement fruité, associant la fraîcheur acidulée de la framboise à la douceur florale de la rose. Cette création élégante offre une tasse harmonieuse, à la fois gourmande et raffinée, idéale pour un moment de plaisir tout en légèreté.
@@ -6369,7 +6104,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr">
+      <c r="S50" s="2" t="inlineStr">
         <is>
           <t>Oolong Framboise
 Oolong Framboise is een geparfumeerde oolong vol delicate fruitigheid, die de frisse zuurheid van frambozen combineert met de bloemige zachtheid van roos. Deze elegante creatie biedt een harmonieuze kop, tegelijk smaakvol en verfijnd, ideaal voor een moment van puur genot in alle lichtheid.
@@ -6387,81 +6122,78 @@
 Consumptie moment: Naar keuze</t>
         </is>
       </c>
-      <c r="T51" s="3" t="inlineStr"/>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>V0847</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>5413393812269</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Pastèque Fraîcheur (ancien nom Couleur Mojito)</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Watermeloen Frisheid</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — pastèque, menthe, sureau</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — watermeloen, munt, vlierbes</t>
         </is>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="I51" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="J52" s="4" t="n">
+      <c r="K51" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K52" s="5" t="n">
+      <c r="L51" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L52" s="4" t="n">
+      <c r="M51" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M52" s="4" t="n">
+      <c r="N51" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="O51" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O52" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0847-Couleur-Mojito-Infusion-de-fruits-pasteque-menthe-Couleur-Mojito-Teatower.jpg?v=1762729500</t>
         </is>
       </c>
-      <c r="Q52" s="2" t="inlineStr">
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-pasteque-menthe-couleur-mojito-teatower</t>
         </is>
       </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="R51" s="2" t="inlineStr">
         <is>
           <t>Pastèque fraîcheur
 C'est l'heure de la sieste. Dehors, l'été pèse lourd. Vous ouvrez le frigo et sortez une pastèque bien fraîche — ce parfum sucré qui embaume la cuisine, ce bruit sourd du couteau qui tranche... Voilà exactement ce que cette infusion capture dans votre tasse. Une tranche d'été, à boire.
@@ -6480,7 +6212,7 @@
 Laissez refroidir quelques heures au frigo avec des glaçons — vous obtiendrez un thé glacé maison qui rivalise avec les plus belles limonades d'été.</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr">
+      <c r="S51" s="2" t="inlineStr">
         <is>
           <t>```html
 Pastèque fraîcheur
@@ -6501,81 +6233,78 @@
 ```</t>
         </is>
       </c>
-      <c r="T52" s="3" t="inlineStr"/>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>V0870</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>5413393813341</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>French Riviera</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>French Riviera</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>Pu erh — églantier, maté, citron</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>Pu-erh — rozenbottel, maté, citroen</t>
         </is>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="I52" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>04/02/2028</t>
         </is>
       </c>
-      <c r="J53" s="4" t="n">
+      <c r="K52" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K53" s="5" t="n">
+      <c r="L52" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L53" s="4" t="n">
+      <c r="M52" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M53" s="4" t="n">
+      <c r="N52" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="O52" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O53" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0870-French-Riviera-Pu-erh-citron-fruit-rouge-French-Riviera-Teatower.jpg?v=1762729534</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr">
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/pu-erh-citron-fruit-rouge-french-riviera-teatower</t>
         </is>
       </c>
-      <c r="R53" s="2" t="inlineStr">
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>French Riviera
 Le French Riviera est un pu-erh parfumé aux notes fraîches et végétales d’églantier, de maté et de citron. Inspirée de l’art de vivre méditerranéen, cette création offre une tasse équilibrée, légèrement tonique et agréablement citronnée, idéale à tout moment de la journée.
@@ -6593,7 +6322,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr">
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>French Riviera
 De French Riviera is een gearomatiseerde pu-erh met frisse en plantaardige tonen van rozenbottel, maté en citroen. Geïnspireerd door de mediterrane levensstijl, biedt deze creatie een gebalanceerd kopje, licht tonisch en aangenaam citroenzuur, ideaal op elk moment van de dag.
@@ -6611,81 +6340,78 @@
 Moment van consumptie: Naar keuze</t>
         </is>
       </c>
-      <c r="T53" s="3" t="inlineStr"/>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>V0875</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>5413393813136</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Evasion Ambrée</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Evasion Ambrée</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Rooibos — orange, cassis, cannelle</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>Rooibos — sinaasappel, zwarte bes, kaneel</t>
         </is>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="I53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>12/12/2027</t>
         </is>
       </c>
-      <c r="J54" s="4" t="n">
+      <c r="K53" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K54" s="5" t="n">
+      <c r="L53" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L54" s="4" t="n">
+      <c r="M53" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M54" s="4" t="n">
+      <c r="N53" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="O53" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O54" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
+      <c r="P53" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0875-Souvenir-de-La-havane-Rooibos-rhum-Souvenir-de-La-Havane-Teatower.jpg?v=1762729544</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr">
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/rooibos-rhum-souvenir-de-la-havane-teatower</t>
         </is>
       </c>
-      <c r="R54" s="2" t="inlineStr">
+      <c r="R53" s="2" t="inlineStr">
         <is>
           <t>Evasion ambrée
 Évasion Ambrée, la nouvelle identité de notre rooibos Souvenir de la Havane. Sans changer sa recette, ce nouveau nom met parfaitement en avant son univers chaleureux, épicé et délicatement fruité, inspiré des ambiances solaires et ambrées.
@@ -6704,7 +6430,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr">
+      <c r="S53" s="2" t="inlineStr">
         <is>
           <t>Evasion ambrée
 Évasion Ambrée, de nieuwe identiteit van onze rooibos Souvenir de la Havane. Zonder de receptuur te wijzigen, brengt deze nieuwe naam perfect zijn warme, gekruide en delicaat fruitige universum naar voren, geïnspireerd door zonrijke en amberen sferen.
@@ -6723,81 +6449,78 @@
 Consumptietijd: Naar keuze</t>
         </is>
       </c>
-      <c r="T54" s="3" t="inlineStr"/>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>V0885</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>5413393814133</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Cococabana</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Cococabana</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>Thé vert — coco, ananas</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Groene thee — kokos, ananas</t>
         </is>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="I54" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>22/02/2028</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n">
+      <c r="K54" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K55" s="5" t="n">
+      <c r="L54" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L55" s="4" t="n">
+      <c r="M54" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M55" s="4" t="n">
+      <c r="N54" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="O54" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O55" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0885-Cococabana-The-vert-coco-Cococabana-Teatower.jpg?v=1762729561</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-coco-cococabana-teatower</t>
         </is>
       </c>
-      <c r="R55" s="2" t="inlineStr">
+      <c r="R54" s="2" t="inlineStr">
         <is>
           <t>Cococabana
 Cococabana est un thé vert parfumé exotique et ensoleillé, qui marie la fraîcheur végétale du thé vert Sencha à la douceur gourmande de la noix de coco et aux notes fruitées de l’ananas. Une invitation à l’évasion, idéale pour une pause dépaysante.
@@ -6815,7 +6538,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr">
+      <c r="S54" s="2" t="inlineStr">
         <is>
           <t>Cococabana
 Cococabana is een exotische en zonnige gearomatiseerde groene thee, die de plantaardige frisheid van Sencha groene thee combineert met de verwennende zoetheid van kokos en de fruitige toetsen van ananas. Een uitnodiging tot ontsnapping, ideaal voor een ontspannende pauze vol exotiek.
@@ -6833,81 +6556,78 @@
 Drinkmoment: Overdag</t>
         </is>
       </c>
-      <c r="T55" s="3" t="inlineStr"/>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>V0889</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>5413393814218</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Maté — grenade, citron</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Maté — granaatappel, citroen</t>
         </is>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="I55" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>04/01/2028</t>
         </is>
       </c>
-      <c r="J56" s="4" t="n">
+      <c r="K55" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K56" s="5" t="n">
+      <c r="L55" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L56" s="4" t="n">
+      <c r="M55" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M56" s="4" t="n">
+      <c r="N55" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="O55" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O56" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
+      <c r="P55" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0889-Granada-Mate-grenade-Granada-Teatower.jpg?v=1762729571</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr">
+      <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/mate-grenade-granada-teatower</t>
         </is>
       </c>
-      <c r="R56" s="2" t="inlineStr">
+      <c r="R55" s="2" t="inlineStr">
         <is>
           <t>Granada
 Granada est un maté parfumé aux notes fraîches et acidulées de grenade et de citron. Tonique et fruité, ce mélange offre une infusion vivifiante et équilibrée, idéale pour stimuler l’énergie et accompagner les débuts de journée.
@@ -6925,7 +6645,7 @@
 Moment de consommation : Matin</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr">
+      <c r="S55" s="2" t="inlineStr">
         <is>
           <t>Granada
 Granada is een gearomatiseerde maté met frisse en pittige noten van granaatappel en citroen. Verkwikkend en fruitig, deze blend biedt een stimulerende en evenwichtige infusie, ideaal om de energie aan te wakkeren en de ochtendrituelen te begeleiden.
@@ -6943,81 +6663,78 @@
 Consumptieмомеnt: Ochtend</t>
         </is>
       </c>
-      <c r="T56" s="3" t="inlineStr"/>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>V0899</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>5413393815062</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité (ancien nom Mumbai Mango) BIO</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité (vroeger Mumbai Mango) BIO</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits BIO — pomme, orange, fraise, mangue</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie BIO — appel, sinaasappel, aardbei, mango</t>
         </is>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="I56" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>24/08/2027</t>
         </is>
       </c>
-      <c r="J57" s="4" t="n">
+      <c r="K56" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K57" s="5" t="n">
+      <c r="L56" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L57" s="4" t="n">
+      <c r="M56" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M57" s="4" t="n">
+      <c r="N56" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="O56" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O57" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0899-Mumbai-Mango-BIO-Infusion-de-fruits-mangue-Mumbai-Mango-BIO-Teatower.jpg?v=1762729586</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr">
+      <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-mangue-mumbai-mango-bio-teatower</t>
         </is>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité
 C'est dimanche matin, la cuisine sent bon les crêpes. Sur la table, les pots de confiture s'alignent comme des promesses colorées — fraise de Wépion, orange amère, compote de pommes du verger. Vous respirez cette symphonie fruitée et souriez. Dans votre tasse, Festival Fruité raconte exactement cette histoire : l'innocence des matins sucrés, la générosité des fruits qui s'entremêlent.
@@ -7037,7 +6754,7 @@
 Astuce : Préparez-la glacée avec une rondelle d'orange fraîche — vos invités penseront à un cocktail sans alcool sophistiqué.</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr">
+      <c r="S56" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité
 Het is zondagochtend, de keuken ruikt naar versgebakken pannenkoeken. Op tafel staan de jampotten op een rij als kleurrijke beloftes — Wépion-aardbeien, bittere sinaasappel, appelcompote uit de boomgaard. Je ademt deze fruitige symfonie in en glimlacht. In je kopje vertelt Festival Fruité precies dit verhaal: de onschuld van zoete ochtenden, de vrijgevigheid van vruchten die elkaar omarmen.
@@ -7057,81 +6774,78 @@
 Tip: Bereid hem ijskoud met een schijfje verse sinaasappel — je gasten zullen denken aan een verfijnde alcoholvrije cocktail.</t>
         </is>
       </c>
-      <c r="T57" s="3" t="inlineStr"/>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>V0900</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>5413393815093</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Bora Bora BIO</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Bora Bora BIO</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Thé noir BIO — pêche, ananas, citronnelle</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee BIO — perzik, ananas, citroengras</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="I57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>13/08/2027</t>
         </is>
       </c>
-      <c r="J58" s="4" t="n">
+      <c r="K57" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="K58" s="5" t="n">
+      <c r="L57" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L58" s="4" t="n">
+      <c r="M57" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="M58" s="4" t="n">
+      <c r="N57" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="O57" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="O58" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
+      <c r="P57" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0900-Bora-Bora-BIO-The-noir-aromatise-passion-Bora-Bora-BIO-Teatower_4f2e9195-322a-4284-a012-885b550ea23f.jpg?v=1762729589</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="inlineStr">
+      <c r="Q57" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-noir-aromatise-passion-bora-bora-bio-teatower</t>
         </is>
       </c>
-      <c r="R58" s="2" t="inlineStr">
+      <c r="R57" s="2" t="inlineStr">
         <is>
           <t>Bora Bora - BIO
 Bora Bora - BIO est un thé noir parfumé biologique aux saveurs exotiques et ensoleillées de pêche, de citronnelle et d’ananas. Évocateur d’évasion et de douceur tropicale, il offre une infusion fruitée et rafraîchissante, idéale pour une dégustation en journée.
@@ -7152,7 +6866,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr">
+      <c r="S57" s="2" t="inlineStr">
         <is>
           <t>Bora Bora - BIO
 Bora Bora - BIO is een biologische gearomatiseerde zwarte thee met exotische en zonnige smaken van perzik, citroengras en ananas. Deze thee roept beelden op van ontsnapping en tropische zachtheid en biedt een fruitige en verfrissende infusie, ideaal voor overdag.
@@ -7173,77 +6887,74 @@
 Consumptie moment: Overdag</t>
         </is>
       </c>
-      <c r="T58" s="3" t="inlineStr"/>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>V0905</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>5413393807913</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Un Noël Vanillé</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Een Gevanielleerde Kerst</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>Oolong, thé blanc &amp; vert — vanille, amande, pomme</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>Oolong, witte &amp; groene thee — vanille, amandel, appel</t>
         </is>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="I58" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K59" s="5" t="n">
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L58" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L59" s="4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="O59" s="4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
+      <c r="M58" s="4" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/Un_noel_vanille.png?v=1769590364</t>
         </is>
       </c>
-      <c r="Q59" s="2" t="inlineStr">
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/un-noel-vanille-oolong-parfume-vanille-teatower</t>
         </is>
       </c>
-      <c r="R59" s="2" t="inlineStr">
+      <c r="R58" s="2" t="inlineStr">
         <is>
           <t>Un Noël Vanillé – Thé Oolong, Blanc &amp; Vert aux Saveurs de Fêtes
 Découvrez Un Noël Vanillé, une infusion raffinée et festive qui marie la douceur de la pomme, la chaleur de la cannelle et la gourmandise de la vanille. Élaborée sur une base de Oolong, de thé blanc et de thé vert, cette création Teatower offre une tasse élégante et délicatement parfumée, parfaite pour les instants cocooning de l’hiver.
@@ -7267,7 +6978,7 @@
 Astuce dégustation : savourez ce thé chaud pour accompagner un dessert de fête, ou froid pour une pause vanillée rafraîchissante. 🎄🍏</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr">
+      <c r="S58" s="2" t="inlineStr">
         <is>
           <t>Un Noël Vanillé – Oolong, Witte &amp; Groene Thee met Feestelijke Smaken
 Ontdek Un Noël Vanillé, een verfijnde en feestelijke infusie die de zoetheid van appel, de warmte van kaneel en de verleidelijke smaak van vanille samenbrengt. Gebaseerd op een blend van Oolong, witte thee en groene thee, biedt deze Teatower-creatie een elegante en delicaat geparfumeerde kop thee, perfect voor knusse wintermomenten.
@@ -7291,77 +7002,70 @@
 Proeverij tip: geniet van deze thee warm als begeleiding bij een feestelijk dessert, of koud voor een verfrissende vanillepauze. 🎄🍏</t>
         </is>
       </c>
-      <c r="T59" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 8.40 € ≠ prix catalogue 7.00 €</t>
-        </is>
-      </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>C0185</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>5413393003858</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>La petite boîte à infusions</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Het kleine infusiedoosje</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Boîte 10 infusettes</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Coffret 10 infusettes sans théine : vanille-cannelle, cerise-amaretto, menthe-rose-lavande, masala chai, canneberge-orange</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>Doosje 10 theezakjes cafeïnevrij: vanille-kaneel, kers-amaretto, munt-roos-lavendel, masala chai, veenbes-sinaasappel</t>
         </is>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="I59" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="4" t="n">
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K60" s="5" t="n">
+      <c r="L59" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L60" s="4" t="n">
+      <c r="M59" s="4" t="n">
         <v>9.43</v>
       </c>
-      <c r="M60" s="4" t="n">
+      <c r="N59" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N60" s="4" t="n">
+      <c r="O59" s="4" t="n">
         <v>5.66</v>
       </c>
-      <c r="O60" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
+      <c r="P59" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003858-La-petite-boite-a-infusions.jpg?v=1762730478</t>
         </is>
       </c>
-      <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="2" t="inlineStr">
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr">
         <is>
           <t>La Petite Boîte à Infusions — 10 Infusettes
 Petite par la taille, grande par les saveurs. Cette boîte tient dans la paume de la main, mais elle contient cinq voyages : les épices chaudes de l'Inde, la douceur de la Méditerranée, les nuits étoilées d'hiver, les cerises de Venise et le calme d'un jardin de roses. 10 infusettes, 5 univers, zéro théine.
@@ -7374,7 +7078,7 @@
 Le petit cadeau qui fait mouche. Format poche, prix doux, effet garanti. À glisser dans une carte, un sac ou sous le sapin.</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr">
+      <c r="S59" s="2" t="inlineStr">
         <is>
           <t>Het Kleine Infusiedoosje — 10 Theezakjes
 Klein van formaat, groot van smaak. Dit doosje past in je handpalm, maar bevat vijf reizen: de warme kruiden van India, de zachtheid van de Middellandse Zee, de sterrenvolle winternachten, de kersen van Venetië en de rust van een rozentuin. 10 theezakjes, 5 werelden, geen cafeïne.
@@ -7387,77 +7091,70 @@
 Het kleine cadeautje dat altijd raak is. Zakformaat, zachte prijs, gegarandeerd effect. Om in een kaart te stoppen, in een tasje of onder de kerstboom.</t>
         </is>
       </c>
-      <c r="T60" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 5.00 € ≠ prix catalogue 10.00 €</t>
-        </is>
-      </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>C0186</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>5413393003841</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>La petite boîte à thés</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Het kleine theedoosje</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Boîte 10 infusettes</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>Coffret 10 infusettes de thé : spéculoos, cerise-jasmin, oolong vanille, orange-amande, pomme-cannelle</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Doosje 10 theezakjes thee: speculaas, kers-jasmijn, oolong vanille, sinaasappel-amandel, appel-kaneel</t>
         </is>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="I60" s="2" t="n">
         <v>298</v>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="4" t="n">
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K61" s="5" t="n">
+      <c r="L60" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L61" s="4" t="n">
+      <c r="M60" s="4" t="n">
         <v>9.43</v>
       </c>
-      <c r="M61" s="4" t="n">
+      <c r="N60" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N61" s="4" t="n">
+      <c r="O60" s="4" t="n">
         <v>5.66</v>
       </c>
-      <c r="O61" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
+      <c r="P60" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003841-Coffret-cacahuete-The-2025.jpg?v=1762730481</t>
         </is>
       </c>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="2" t="inlineStr">
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr">
         <is>
           <t>La Petite Boîte à Thés — 10 Infusettes
 Pour ceux qui préfèrent la profondeur du thé à la légèreté de l'infusion. Cette petite boîte réunit cinq thés d'exception — du spéculoos belge à la pâtisserie orientale, en passant par la vanille de Noël et la pomme-cannelle de mamie. 10 sachets, 5 caractères, une seule certitude : vous allez trouver votre favori.
@@ -7470,7 +7167,7 @@
 Un petit prix, un grand effet. À offrir sans raison particulière — ou parce que les meilleurs cadeaux sont ceux qu'on n'attend pas.</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr">
+      <c r="S60" s="2" t="inlineStr">
         <is>
           <t>De Kleine Theedoos — 10 Theezakjes
 Voor wie de diepte van thee verkiest boven de lichtheid van tisanes. Deze kleine doos verenigt vijf uitzonderlijke theeën — van Belgische speculoos tot oosterse patisserie, via kerstvanille en oma's appel-kaneel. 10 zakjes, 5 karakters, één zekerheid: u gaat uw favoriet vinden.
@@ -7483,77 +7180,70 @@
 Een kleine prijs, een groot effect. Om cadeau te geven zonder bijzondere reden — of omdat de beste geschenken die zijn die men niet verwacht.</t>
         </is>
       </c>
-      <c r="T61" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 5.00 € ≠ prix catalogue 10.00 €</t>
-        </is>
-      </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>C0187</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>5413393003865</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Coffret découverte de Noël</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Kerst ontdekkingsbox</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Coffret 25 infusettes</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>Coffret 25 infusettes : cacao-noisette, rooibos amande, orange-cannelle, oolong vanille, canneberge-orange</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>Box 25 theezakjes: cacao-hazelnoot, rooibos amandel, sinaasappel-kaneel, oolong vanille, veenbes-sinaasappel</t>
         </is>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="I61" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="4" t="n">
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="K62" s="5" t="n">
+      <c r="L61" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L62" s="4" t="n">
+      <c r="M61" s="4" t="n">
         <v>14.15</v>
       </c>
-      <c r="M62" s="4" t="n">
+      <c r="N61" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="O61" s="4" t="n">
         <v>8.49</v>
       </c>
-      <c r="O62" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="P62" s="2" t="inlineStr">
+      <c r="P61" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003865-Coffret-decouverte-de-Noel-2025.jpg?v=1762730484</t>
         </is>
       </c>
-      <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="2" t="inlineStr">
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr">
         <is>
           <t>Coffret Découverte de Noël — 25 Infusettes Festives
 Imaginez : dehors, le froid de décembre. Dedans, vos mains enveloppent une tasse fumante aux parfums de cannelle, de cacao et d'orange confite. Le Coffret Découverte de Noël, c'est ce moment-là — multiplié par 25. Cinq créations Teatower réunies dans un seul coffret, pour transformer chaque matin de décembre en petit rituel gourmand.
@@ -7570,7 +7260,7 @@
 Pour qui ? Pour la personne qui vous dit toujours "rien, merci" quand vous demandez ce qui lui ferait plaisir. Ce coffret, c'est la réponse parfaite.</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr">
+      <c r="S61" s="2" t="inlineStr">
         <is>
           <t>\
 \Kerst Ontdekkingsdoos – 25 Feestelijke Infusettes\
@@ -7606,73 +7296,70 @@
 \</t>
         </is>
       </c>
-      <c r="T62" s="3" t="inlineStr"/>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>C0188</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>5413393003872</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>La hotte de Noël</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>De kerstsok</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Coffret 4 × 50 g + pince</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>Coffret 4 × 50 g vrac + pince à thé : cacao-noisette, orange-cannelle, rooibos amande, canneberge-orange</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>Box 4 × 50 g losse thee + theeklem: cacao-hazelnoot, sinaasappel-kaneel, rooibos amandel, veenbes-sinaasappel</t>
         </is>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="I62" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="4" t="n">
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="K63" s="5" t="n">
+      <c r="L62" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L63" s="4" t="n">
+      <c r="M62" s="4" t="n">
         <v>37.74</v>
       </c>
-      <c r="M63" s="4" t="n">
+      <c r="N62" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="N63" s="4" t="n">
+      <c r="O62" s="4" t="n">
         <v>22.64</v>
       </c>
-      <c r="O63" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003872-La-hotte-de-Noel.jpg?v=1762730486</t>
         </is>
       </c>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="2" t="inlineStr">
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr">
         <is>
           <t>La Hotte de Noël — Coffret 4 Infusions en Vrac + Pince à Thé
 200 grammes de pur bonheur hivernal. Ouvrez la hotte et laissez les parfums vous envahir : le cacao grillé du Trésor des Lutins, les épices chaudes de l'Offrande des Rois Mages, l'amande douce de la Gourmandise de Noël, et la canneberge pétillante de la Féérie d'Hiver. Quatre boîtes, une pince à thé, des semaines de plaisir.
@@ -7687,7 +7374,7 @@
 Pour les amoureux du vrai thé. Ce coffret est fait pour ceux qui prennent le temps d'infuser, de sentir, de savourer.</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr">
+      <c r="S62" s="2" t="inlineStr">
         <is>
           <t>De Kerstzak — Geschenkset 4 Losse Infusies + Theeklem
 200 gram puur wintergeluk. Open de zak en laat de geuren je overweldigen: de geroosterde cacao van Schat der Kaboutertjes, de warme kruiden van Geschenk der Wijzen, de zoete amandel van Kerstlekkernij, en de sprankelende cranberry van Wintersprookje. Vier doosjes, één theeklem, weken vol genot.
@@ -7702,73 +7389,70 @@
 Voor de liefhebbers van echte thee. Deze geschenkset is gemaakt voor wie de tijd neemt om te laten trekken, te ruiken, te proeven.</t>
         </is>
       </c>
-      <c r="T63" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 20.00 € ≠ prix catalogue 40.00 €</t>
-        </is>
-      </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>C0191</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>5413393004350</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Trésor des lutins</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Schat van de elfen</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Boîte 50 g</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — chocolat, noisette</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — chocolade, hazelnoot</t>
         </is>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="I63" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="4" t="n">
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K64" s="5" t="n">
+      <c r="L63" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L64" s="4" t="n">
+      <c r="M63" s="4" t="n">
         <v>9.43</v>
       </c>
-      <c r="M64" s="4" t="n">
+      <c r="N63" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N64" s="4" t="n">
+      <c r="O63" s="4" t="n">
         <v>5.66</v>
       </c>
-      <c r="O64" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003872_3.png?v=1768229545</t>
         </is>
       </c>
-      <c r="Q64" s="2" t="inlineStr"/>
-      <c r="R64" s="2" t="inlineStr">
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr">
         <is>
           <t>Trésor des Lutins
 Au fond de l'atelier du Père Noël, les lutins cachent un secret. Quand les rires s'estompent et que l'ouvrage avance, ils s'accordent une pause autour d'un bol fumant qui sent la noisette grillée et le cacao. C'est leur trésor, celui qui réchauffe les cœurs avant la grande distribution. Une recette transmise de lutin en lutin, pour les moments où l'on a besoin de croire encore un peu à la magie.
@@ -7794,7 +7478,7 @@
 Astuce gourmande : Ajoutez une pointe de lait d'amande pour intensifier la note noisette de cette infusion de Noël.</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr">
+      <c r="S63" s="2" t="inlineStr">
         <is>
           <t>Schatt van de Elfen – Kerstinfusie Hazelnoot &amp; Cacao (Theïne Vrij)
 Stap binnen in de betoverende werkplaats van de Kerstman: Schatt van de Elfen combineert de zachtheid van geroosterde hazelnoot met cacao en winterfruit, voor een heerlijke en natuurlijk theïnevrije kerstinfusie.
@@ -7813,73 +7497,74 @@
 Tip voor proeven: ideaal op elk moment van de dag voor een zachte en gastronomische pauze.</t>
         </is>
       </c>
-      <c r="T64" s="3" t="inlineStr"/>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>C0192</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr"/>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>5413393004367</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Gourmandise de Noël</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Kerstlekkernij</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Boîte 50 g</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>Rooibos — amande, ananas</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Rooibos — amandel, ananas</t>
         </is>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="I64" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="4" t="n">
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K65" s="5" t="n">
+      <c r="L64" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L65" s="4" t="n">
+      <c r="M64" s="4" t="n">
         <v>9.43</v>
       </c>
-      <c r="M65" s="4" t="n">
+      <c r="N64" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N65" s="4" t="n">
+      <c r="O64" s="4" t="n">
         <v>5.66</v>
       </c>
-      <c r="O65" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
+      <c r="P64" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003872_4.png?v=1768230036</t>
         </is>
       </c>
-      <c r="Q65" s="2" t="inlineStr">
+      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/rooibos-amande-gourmandise-de-noel-teatower-1</t>
         </is>
       </c>
-      <c r="R65" s="2" t="inlineStr">
+      <c r="R64" s="2" t="inlineStr">
         <is>
           <t>Gourmandise de Noël – Rooibos Pâte d’Amande &amp; Ananas
 Laissez-vous séduire par Gourmandise de Noël, un rooibos festif mêlant la douceur de la pâte d’amande à la fraîcheur fruitée des morceaux d’ananas. Une infusion sans théine, idéale pour les instants cocooning de l’hiver.
@@ -7902,7 +7587,7 @@
 Astuce dégustation : savourez chaud, accompagné d’un biscuit de Noël, pour une pause douce et gourmande. 🎄</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr">
+      <c r="S64" s="2" t="inlineStr">
         <is>
           <t>Kerstlekkernij – Rooibos Amandelpasta &amp; Ananas
 Laat u verleiden door Kerstlekkernij, een feestelijke rooibos die de zoetheid van amandelpasta combineert met de fruitige frisheid van ananasstukjes. Een cafeïnevrije infusie, ideaal voor knusse wintermomenten.
@@ -7921,73 +7606,70 @@
 Degustatietip: geniet warm, samen met een kerstkoekje, voor een zachte en heerlijke pauze. 🎄</t>
         </is>
       </c>
-      <c r="T65" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 7.00 € ≠ prix catalogue 10.00 €</t>
-        </is>
-      </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>C0193</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr"/>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>5413393004374</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Féérie d'Hiver</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Wintersprookje</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Boîte 50 g</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — canneberge, orange</t>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — veenbes, sinaasappel</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="I65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="4" t="n">
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="K66" s="5" t="n">
+      <c r="L65" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="L66" s="4" t="n">
+      <c r="M65" s="4" t="n">
         <v>9.43</v>
       </c>
-      <c r="M66" s="4" t="n">
+      <c r="N65" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N66" s="4" t="n">
+      <c r="O65" s="4" t="n">
         <v>5.66</v>
       </c>
-      <c r="O66" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
+      <c r="P65" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003872_5.png?v=1768229198</t>
         </is>
       </c>
-      <c r="Q66" s="2" t="inlineStr"/>
-      <c r="R66" s="2" t="inlineStr">
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr">
         <is>
           <t>Féérie d'Hiver
 Il neige dehors, et dans votre cuisine flotte déjà ce parfum de fête. Vous versez l'eau frémissante sur les canneberges écarlates et les écorces d'orange. Cinq minutes plus tard, votre tasse se pare d'un rouge rubis profond — comme les guirlandes qui ornent déjà le sapin. C'est Noël qui commence, une gorgée à la fois.
@@ -8014,7 +7696,7 @@
 Astuce gourmande : Ajoutez quelques cuillères de cette infusion dans votre vin chaud maison — les canneberges et l'orange transformeront votre breuvage en véritable élixir de fête.</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr">
+      <c r="S65" s="2" t="inlineStr">
         <is>
           <t>Féérie d'Hiver
 Het sneeuwt buiten, en in uw keuken hangt al die feestelijke geur. U giet het borrelende water over de scharlakenrode cranberry's en de sinaasappelschillen. Vijf minuten later tooit uw kopje zich in een diep robijnrood — zoals de slingers die al de kerstboom opfleuren. Zo begint Kerstmis, slok voor slok.
@@ -8041,35 +7723,31 @@
 Lekkere tip: Voeg enkele lepels van deze infusie toe aan uw zelfgemaakte glühwein — de cranberry's en sinaasappel transformeren uw drank tot een waar feestelixer.</t>
         </is>
       </c>
-      <c r="T66" s="3" t="inlineStr">
-        <is>
-          <t>Prix Shopify actuel 5.00 € ≠ prix catalogue 10.00 €</t>
-        </is>
-      </c>
     </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>65 références</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" s="10">
-        <f>SUM(H2:H66)</f>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>64 références</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" s="6">
+        <f>SUM(I2:I65)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T66"/>
+  <autoFilter ref="A1:S65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/veepee/Veepee - stock disponible vente privee.xlsx
+++ b/veepee/Veepee - stock disponible vente privee.xlsx
@@ -5553,22 +5553,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>V0742</t>
+          <t>V0732</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>5413393800358</t>
+          <t>5413393800693</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Ange Gardien</t>
+          <t>Gourmandise de Noël</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Beschermengel</t>
+          <t>Kerstlekkernij</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5579,48 +5579,161 @@
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Oolong — fraise, goji</t>
+          <t>Rooibos — amande, ananas</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Oolong — aardbei, goji</t>
+          <t>Rooibos — amandel, ananas</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>22/02/2028</t>
-        </is>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>0.06</v>
       </c>
       <c r="M46" s="4" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/Gourmandise_de_noel.png?v=1769590512</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>https://teatower.com/products/rooibos-amande-gourmandise-de-noel-teatower</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Gourmandise de Noël – Rooibos Pâte d’Amande &amp; Ananas
+Laissez-vous séduire par Gourmandise de Noël, un rooibos festif mêlant la douceur de la pâte d’amande à la fraîcheur fruitée des morceaux d’ananas. Une infusion sans théine, idéale pour les instants cocooning de l’hiver.
+Recette &amp; préparation
+•
+Contenu : vrac 100 Gr
+•
+Dosage : 1–2 c. à café pour 250 ml
+•
+Température : 95 °C
+•
+Infusion : 7–10 minutes
+Ingrédients
+• Rooibos d’Afrique du Sud (69%)
+• Morceaux d’ananas (sucre de canne, ananas, acide citrique)
+• Arôme
+• Amandes hachées et effilées**
+• Sucre perlé
+**Ingrédient allergène : amandes.
+Astuce dégustation : savourez chaud, accompagné d’un biscuit de Noël, pour une pause douce et gourmande. 🎄</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Kerstlekkernij – Rooibos Amandelspijs &amp; Ananas
+Laat je verleiden door Kerstlekkernij, een feestelijke rooibos die de zachtheid van amandelspijs vermengt met de fruitige frisheid van ananasstuktjes. Een infusie zonder cafeïne, ideaal voor warme winterse momenten vol gezelligheid.
+Recept &amp; bereiding
+•
+Inhoud: los 100 gr
+•
+Dosering: 1–2 theelepels voor 250 ml
+•
+Temperatuur: 95 °C
+•
+Trektijd: 7–10 minuten
+Ingrediënten
+• Rooibos uit Zuid-Afrika (69%)
+• Ananasstuktjes (rietsuiker, ananas, citroenzuur)
+• Aroma
+• Gehakte en gefileerde amandelen**
+• Parelsulker
+**Allergeen ingrediënt: amandelen.
+Proeftip: geniet warm, met een kerstkoekje erbij, voor een zachte en heerlijke pauze. 🎄</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>V0742</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>5413393800358</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Ange Gardien</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Beschermengel</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>100 g vrac</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Oolong — fraise, goji</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Oolong — aardbei, goji</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>22/02/2028</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M47" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N46" s="4" t="n">
+      <c r="N47" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O46" s="4" t="n">
+      <c r="O47" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0742-Ange-Gardien-Oolong-mangue-fraise-Ange-Gardien-Teatower.jpg?v=1762729392</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="inlineStr">
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/oolong-mangue-fraise-ange-gardien-teatower</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
+      <c r="R47" s="2" t="inlineStr">
         <is>
           <t>Ange Gardien
 Le thé oolong parfumé Ange Gardien marie délicatement Goji – Fraise pour une tasse fruitée, douce et réconfortante. Un oolong faible en théine, parfait pour une pause gourmande à tout moment de la journée.
@@ -5638,7 +5751,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr">
+      <c r="S47" s="2" t="inlineStr">
         <is>
           <t>Ange Gardien
 De geparfumeerde oolong thee Ange Gardien combineert delicaat Goji – Aardbei voor een fruitige, zachte en troostende kop thee. Een oolong arm aan cafeïne, perfect voor een lekkere pauze op elk moment van de dag.
@@ -5657,77 +5770,77 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>V0788</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>5413393800624</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Japan Sencha Yamato</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Japan Sencha Yamato</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>50g vrac</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>Thé vert nature — Sencha du Japon</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Groene thee natuur — Japanse Sencha</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="I48" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>01/04/2028</t>
         </is>
       </c>
-      <c r="K47" s="4" t="n">
+      <c r="K48" s="4" t="n">
         <v>18.5</v>
       </c>
-      <c r="L47" s="5" t="n">
+      <c r="L48" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M47" s="4" t="n">
+      <c r="M48" s="4" t="n">
         <v>17.45</v>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N48" s="4" t="n">
         <v>11.1</v>
       </c>
-      <c r="O47" s="4" t="n">
+      <c r="O48" s="4" t="n">
         <v>10.47</v>
       </c>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0788-Japan-Sencha-Yamato-Finest-quality-The-vert-nature-Japan-Sencha-Yamato-Teatower.jpg?v=1762729417</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr">
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-nature-japan-sencha-yamato-teatower</t>
         </is>
       </c>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>Japan Sencha Yamato – Finest quality
 Le Japan Sencha Yamato – Finest quality est un thé vert d’exception, issu de feuilles de Sencha haut de gamme du Japon. Référence emblématique des thés verts japonais, il séduit par son caractère à la fois végétal, frais et intensément aromatique.
@@ -5745,7 +5858,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr">
+      <c r="S48" s="2" t="inlineStr">
         <is>
           <t>Japan Sencha Yamato – Finest quality
 De Japan Sencha Yamato – Finest quality is een uitzonderlijke groene thee, afkomstig van premium Sencha bladeren uit Japan. Deze emblematische referentie van Japanse groene theeën bekoort door zijn karakter dat tegelijk vegetaal, fris en intens aromatisch is.
@@ -5764,77 +5877,77 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>V0793</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>5413393800341</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Orangipane</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Orangipane</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Thé vert — orange, amande, fleur d'oranger</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Groene thee — sinaasappel, amandel, oranjebloesem</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="I49" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>18/03/2028</t>
         </is>
       </c>
-      <c r="K48" s="4" t="n">
+      <c r="K49" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="L48" s="5" t="n">
+      <c r="L49" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M48" s="4" t="n">
+      <c r="M49" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N48" s="4" t="n">
+      <c r="N49" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O48" s="4" t="n">
+      <c r="O49" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P48" s="2" t="inlineStr">
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0793-Orangipane-The-vert-orange-amande-Orangipane-Teatower.jpg?v=1762729419</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="inlineStr">
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-orange-amande-orangipane-teatower</t>
         </is>
       </c>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>Orangipane
 L’Orangipane est un thé vert parfumé gourmand et chaleureux,
@@ -5860,7 +5973,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr">
+      <c r="S49" s="2" t="inlineStr">
         <is>
           <t>Orangipane
 Orangipane is een geparfumeerde groene thee met een verwarmende, verwennende smaak,
@@ -5887,77 +6000,77 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>V0822</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>5413393808422</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Sous les cocotiers</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sous les cocotiers</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — coco, melon</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — kokos, meloen</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="I50" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>11/02/2028</t>
         </is>
       </c>
-      <c r="K49" s="4" t="n">
+      <c r="K50" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="L49" s="5" t="n">
+      <c r="L50" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M49" s="4" t="n">
+      <c r="M50" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N49" s="4" t="n">
+      <c r="N50" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O49" s="4" t="n">
+      <c r="O50" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P49" s="2" t="inlineStr">
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0822-Sous-les-cocotiers-Infusion-de-fruits-coco-melon-Sous-les-cocotiers-Teatower.jpg?v=1762729457</t>
         </is>
       </c>
-      <c r="Q49" s="2" t="inlineStr">
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-coco-melon-sous-les-cocotiers-teatower</t>
         </is>
       </c>
-      <c r="R49" s="2" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>Sous les cocotiers
 Premier jour de vacances. Vous êtes allongé sur le sable chaud, une brise légère apporte un parfum de coco et de melon. Quelqu’un vous tend un verre fraîchement pressé. Vous fermez les yeux et souriez. Sous les cocotiers, c’est ce moment-là — en infusion.
@@ -5986,7 +6099,7 @@
 Le saviez-vous ? Le cocotier est appelé “l’arbre de vie” car chaque partie est utilisable : l’eau, le lait, la chair, l’huile, la coque (charbon), les feuilles (toitures), et même les fibres (cordage). Un seul cocotier peut produire pendant 80 ans. C’est la nature à son meilleur.</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr">
+      <c r="S50" s="2" t="inlineStr">
         <is>
           <t>Onder de Kokospalmen
 Eerste vakantiedag. Je ligt languit op het warme zand, een lichte bries brengt de geur van kokos en meloen. Iemand reikt je een vers geperst glas aan. Je sluit je ogen en glimlacht. Onder de Kokospalmen, dat is dit moment — als infusie.
@@ -6016,77 +6129,77 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>V0838</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>5413393812023</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>framboise rose</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>framboos roos</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Oolong — framboise, rose</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>Oolong — framboos, roos</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="I51" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>27/12/2027</t>
         </is>
       </c>
-      <c r="K50" s="4" t="n">
+      <c r="K51" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="L50" s="5" t="n">
+      <c r="L51" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M50" s="4" t="n">
+      <c r="M51" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N50" s="4" t="n">
+      <c r="N51" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O50" s="4" t="n">
+      <c r="O51" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P50" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0838-Oolong-Framboise-Oolong-Framboise-Teatower.jpg?v=1762729482</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="inlineStr">
+      <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/oolong-framboise-teatower</t>
         </is>
       </c>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="R51" s="2" t="inlineStr">
         <is>
           <t>Oolong Framboise
 Oolong Framboise est un oolong parfumé délicatement fruité, associant la fraîcheur acidulée de la framboise à la douceur florale de la rose. Cette création élégante offre une tasse harmonieuse, à la fois gourmande et raffinée, idéale pour un moment de plaisir tout en légèreté.
@@ -6104,7 +6217,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr">
+      <c r="S51" s="2" t="inlineStr">
         <is>
           <t>Oolong Framboise
 Oolong Framboise is een geparfumeerde oolong vol delicate fruitigheid, die de frisse zuurheid van frambozen combineert met de bloemige zachtheid van roos. Deze elegante creatie biedt een harmonieuze kop, tegelijk smaakvol en verfijnd, ideaal voor een moment van puur genot in alle lichtheid.
@@ -6123,77 +6236,77 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>V0847</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>5413393812269</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Pastèque Fraîcheur (ancien nom Couleur Mojito)</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Watermeloen Frisheid</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits — pastèque, menthe, sureau</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie — watermeloen, munt, vlierbes</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I52" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="K51" s="4" t="n">
+      <c r="K52" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="L51" s="5" t="n">
+      <c r="L52" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M51" s="4" t="n">
+      <c r="M52" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N51" s="4" t="n">
+      <c r="N52" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O51" s="4" t="n">
+      <c r="O52" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P51" s="2" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0847-Couleur-Mojito-Infusion-de-fruits-pasteque-menthe-Couleur-Mojito-Teatower.jpg?v=1762729500</t>
         </is>
       </c>
-      <c r="Q51" s="2" t="inlineStr">
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-pasteque-menthe-couleur-mojito-teatower</t>
         </is>
       </c>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>Pastèque fraîcheur
 C'est l'heure de la sieste. Dehors, l'été pèse lourd. Vous ouvrez le frigo et sortez une pastèque bien fraîche — ce parfum sucré qui embaume la cuisine, ce bruit sourd du couteau qui tranche... Voilà exactement ce que cette infusion capture dans votre tasse. Une tranche d'été, à boire.
@@ -6212,7 +6325,7 @@
 Laissez refroidir quelques heures au frigo avec des glaçons — vous obtiendrez un thé glacé maison qui rivalise avec les plus belles limonades d'été.</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr">
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>```html
 Pastèque fraîcheur
@@ -6234,77 +6347,77 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>V0870</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>5413393813341</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>French Riviera</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>French Riviera</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Pu erh — églantier, maté, citron</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>Pu-erh — rozenbottel, maté, citroen</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I53" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>04/02/2028</t>
         </is>
       </c>
-      <c r="K52" s="4" t="n">
+      <c r="K53" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="L52" s="5" t="n">
+      <c r="L53" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M52" s="4" t="n">
+      <c r="M53" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N52" s="4" t="n">
+      <c r="N53" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O52" s="4" t="n">
+      <c r="O53" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P52" s="2" t="inlineStr">
+      <c r="P53" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0870-French-Riviera-Pu-erh-citron-fruit-rouge-French-Riviera-Teatower.jpg?v=1762729534</t>
         </is>
       </c>
-      <c r="Q52" s="2" t="inlineStr">
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/pu-erh-citron-fruit-rouge-french-riviera-teatower</t>
         </is>
       </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="R53" s="2" t="inlineStr">
         <is>
           <t>French Riviera
 Le French Riviera est un pu-erh parfumé aux notes fraîches et végétales d’églantier, de maté et de citron. Inspirée de l’art de vivre méditerranéen, cette création offre une tasse équilibrée, légèrement tonique et agréablement citronnée, idéale à tout moment de la journée.
@@ -6322,7 +6435,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr">
+      <c r="S53" s="2" t="inlineStr">
         <is>
           <t>French Riviera
 De French Riviera is een gearomatiseerde pu-erh met frisse en plantaardige tonen van rozenbottel, maté en citroen. Geïnspireerd door de mediterrane levensstijl, biedt deze creatie een gebalanceerd kopje, licht tonisch en aangenaam citroenzuur, ideaal op elk moment van de dag.
@@ -6341,77 +6454,77 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>V0875</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>5413393813136</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Evasion Ambrée</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Evasion Ambrée</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>Rooibos — orange, cassis, cannelle</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Rooibos — sinaasappel, zwarte bes, kaneel</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="I54" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>12/12/2027</t>
         </is>
       </c>
-      <c r="K53" s="4" t="n">
+      <c r="K54" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="L53" s="5" t="n">
+      <c r="L54" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M53" s="4" t="n">
+      <c r="M54" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N53" s="4" t="n">
+      <c r="N54" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O53" s="4" t="n">
+      <c r="O54" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P53" s="2" t="inlineStr">
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0875-Souvenir-de-La-havane-Rooibos-rhum-Souvenir-de-La-Havane-Teatower.jpg?v=1762729544</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/rooibos-rhum-souvenir-de-la-havane-teatower</t>
         </is>
       </c>
-      <c r="R53" s="2" t="inlineStr">
+      <c r="R54" s="2" t="inlineStr">
         <is>
           <t>Evasion ambrée
 Évasion Ambrée, la nouvelle identité de notre rooibos Souvenir de la Havane. Sans changer sa recette, ce nouveau nom met parfaitement en avant son univers chaleureux, épicé et délicatement fruité, inspiré des ambiances solaires et ambrées.
@@ -6430,7 +6543,7 @@
 Moment de consommation : Au choix</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr">
+      <c r="S54" s="2" t="inlineStr">
         <is>
           <t>Evasion ambrée
 Évasion Ambrée, de nieuwe identiteit van onze rooibos Souvenir de la Havane. Zonder de receptuur te wijzigen, brengt deze nieuwe naam perfect zijn warme, gekruide en delicaat fruitige universum naar voren, geïnspireerd door zonrijke en amberen sferen.
@@ -6450,77 +6563,77 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>V0885</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>5413393814133</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Cococabana</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Cococabana</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Thé vert — coco, ananas</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Groene thee — kokos, ananas</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I55" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>22/02/2028</t>
         </is>
       </c>
-      <c r="K54" s="4" t="n">
+      <c r="K55" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="L54" s="5" t="n">
+      <c r="L55" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M54" s="4" t="n">
+      <c r="M55" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N54" s="4" t="n">
+      <c r="N55" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O54" s="4" t="n">
+      <c r="O55" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P54" s="2" t="inlineStr">
+      <c r="P55" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0885-Cococabana-The-vert-coco-Cococabana-Teatower.jpg?v=1762729561</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr">
+      <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-vert-coco-cococabana-teatower</t>
         </is>
       </c>
-      <c r="R54" s="2" t="inlineStr">
+      <c r="R55" s="2" t="inlineStr">
         <is>
           <t>Cococabana
 Cococabana est un thé vert parfumé exotique et ensoleillé, qui marie la fraîcheur végétale du thé vert Sencha à la douceur gourmande de la noix de coco et aux notes fruitées de l’ananas. Une invitation à l’évasion, idéale pour une pause dépaysante.
@@ -6538,7 +6651,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr">
+      <c r="S55" s="2" t="inlineStr">
         <is>
           <t>Cococabana
 Cococabana is een exotische en zonnige gearomatiseerde groene thee, die de plantaardige frisheid van Sencha groene thee combineert met de verwennende zoetheid van kokos en de fruitige toetsen van ananas. Een uitnodiging tot ontsnapping, ideaal voor een ontspannende pauze vol exotiek.
@@ -6557,77 +6670,77 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>V0889</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>5413393814218</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F55" s="2" t="n"/>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>Maté — grenade, citron</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Maté — granaatappel, citroen</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="I56" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>04/01/2028</t>
         </is>
       </c>
-      <c r="K55" s="4" t="n">
+      <c r="K56" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="L55" s="5" t="n">
+      <c r="L56" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M55" s="4" t="n">
+      <c r="M56" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N55" s="4" t="n">
+      <c r="N56" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O55" s="4" t="n">
+      <c r="O56" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P55" s="2" t="inlineStr">
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0889-Granada-Mate-grenade-Granada-Teatower.jpg?v=1762729571</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr">
+      <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/mate-grenade-granada-teatower</t>
         </is>
       </c>
-      <c r="R55" s="2" t="inlineStr">
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>Granada
 Granada est un maté parfumé aux notes fraîches et acidulées de grenade et de citron. Tonique et fruité, ce mélange offre une infusion vivifiante et équilibrée, idéale pour stimuler l’énergie et accompagner les débuts de journée.
@@ -6645,7 +6758,7 @@
 Moment de consommation : Matin</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr">
+      <c r="S56" s="2" t="inlineStr">
         <is>
           <t>Granada
 Granada is een gearomatiseerde maté met frisse en pittige noten van granaatappel en citroen. Verkwikkend en fruitig, deze blend biedt een stimulerende en evenwichtige infusie, ideaal om de energie aan te wakkeren en de ochtendrituelen te begeleiden.
@@ -6664,77 +6777,184 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>V0891</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>5413393814867</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Trésor des lutins</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Schat van de elfen</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>100 g vrac</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Infusion de fruits — chocolat, noisette</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Vruchteninfusie — chocolade, hazelnoot</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/Tresor_des_lutins.png?v=1769592963</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>https://teatower.com/products/infusion-de-fruits-chocolat-noisette-tresor-des-lutins-teatower</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Trésor des Lutins
+Au fond de l'atelier du Père Noël, derrière les piles de cadeaux, les lutins cachent un secret : une recette de fruits d'hiver, de cacao et de noisette grillée qu'ils sirotent en riant quand personne ne regarde. C'est cette recette que nous avons volée pour vous. Le Trésor des Lutins, c'est Noël en une gorgée — gourmand, réconfortant, et naturellement sans théine.
+Les éclats de cacao et les feuilles d'amandier apportent une profondeur chocolatée, tandis que les pétales de rose et les fleurs de carthame ajoutent une touche de couleur et de délicatesse. La tasse est ambrée, le parfum envoûtant, et chaque gorgée rappelle les bonbons de Noël qu'on volait dans le sapin.
+Recette &amp; préparation
+•
+Contenu : 100 g en vrac
+•
+Dosage : 1 à 2 c. à café pour 250 ml
+•
+Température : 95 °C
+•
+Infusion : 8 à 10 minutes — laissez le temps aux arômes de se libérer
+Ingrédients
+Morceaux de pomme (pomme, acide citrique), écorces et brisures de cacao, feuilles d'amandier, pétales de rose rouge, bleuet blanc, fleurs de carthame, arôme naturel.
+Allergène : amandes.
+Astuce : ajoutez une pointe de lait végétal pour un effet chocolat chaud d'hiver — les enfants adorent.</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>Trésor des Lutins
+Diep in de werkplaats van de Kerstman, achter de stapels cadeaus, verbergen de kabouters een geheim: een recept van wintervruchten, cacao en geroosterde hazelnoot dat ze lachend nippen wanneer niemand kijkt. Dit recept hebben we voor u gestolen. De Trésor des Lutins, dat is Kerstmis in één teug — verwennend, troostend, en natuurlijk zonder cafeïne.
+De cacaoschilfers en amandelbladeren brengen een chocoladeachtige diepte, terwijl de rozenblaadjes en saffloerbloemen een vleugje kleur en finesse toevoegen. De kop is amber, het aroma betoverend, en elke teug herinnert aan de kerstbonbons die we stiekem uit de boom pikten.
+Recept &amp; bereiding
+•
+Inhoud: 100 g los
+•
+Dosering: 1 tot 2 theelepels voor 250 ml
+•
+Temperatuur: 95 °C
+•
+Infusie: 8 tot 10 minuten — geef de aroma's de tijd om vrij te komen
+Ingrediënten
+Appelstukjes (appel, citroenzuur), cacaoschillen en -brokken, amandelbladeren, rode rozenblaadjes, witte korenbloem, saffloerbloemen, natuurlijk aroma.
+Allergeen: amandelen.
+Tip: voeg een scheutje plantaardige melk toe voor een warme chocolademelk-effect — kinderen zijn er dol op.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>V0899</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>5413393815062</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité (ancien nom Mumbai Mango) BIO</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité (vroeger Mumbai Mango) BIO</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>Infusion de fruits BIO — pomme, orange, fraise, mangue</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>Vruchteninfusie BIO — appel, sinaasappel, aardbei, mango</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="I58" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>24/08/2027</t>
         </is>
       </c>
-      <c r="K56" s="4" t="n">
+      <c r="K58" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="L56" s="5" t="n">
+      <c r="L58" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M56" s="4" t="n">
+      <c r="M58" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N58" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O56" s="4" t="n">
+      <c r="O58" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P56" s="2" t="inlineStr">
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0899-Mumbai-Mango-BIO-Infusion-de-fruits-mangue-Mumbai-Mango-BIO-Teatower.jpg?v=1762729586</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr">
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/infusion-de-fruits-mangue-mumbai-mango-bio-teatower</t>
         </is>
       </c>
-      <c r="R56" s="2" t="inlineStr">
+      <c r="R58" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité
 C'est dimanche matin, la cuisine sent bon les crêpes. Sur la table, les pots de confiture s'alignent comme des promesses colorées — fraise de Wépion, orange amère, compote de pommes du verger. Vous respirez cette symphonie fruitée et souriez. Dans votre tasse, Festival Fruité raconte exactement cette histoire : l'innocence des matins sucrés, la générosité des fruits qui s'entremêlent.
@@ -6754,7 +6974,7 @@
 Astuce : Préparez-la glacée avec une rondelle d'orange fraîche — vos invités penseront à un cocktail sans alcool sophistiqué.</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr">
+      <c r="S58" s="2" t="inlineStr">
         <is>
           <t>Festival Fruité
 Het is zondagochtend, de keuken ruikt naar versgebakken pannenkoeken. Op tafel staan de jampotten op een rij als kleurrijke beloftes — Wépion-aardbeien, bittere sinaasappel, appelcompote uit de boomgaard. Je ademt deze fruitige symfonie in en glimlacht. In je kopje vertelt Festival Fruité precies dit verhaal: de onschuld van zoete ochtenden, de vrijgevigheid van vruchten die elkaar omarmen.
@@ -6775,77 +6995,77 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>V0900</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>5413393815093</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Bora Bora BIO</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Bora Bora BIO</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Thé noir BIO — pêche, ananas, citronnelle</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>Zwarte thee BIO — perzik, ananas, citroengras</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="I59" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>13/08/2027</t>
         </is>
       </c>
-      <c r="K57" s="4" t="n">
+      <c r="K59" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="L57" s="5" t="n">
+      <c r="L59" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M57" s="4" t="n">
+      <c r="M59" s="4" t="n">
         <v>9.91</v>
       </c>
-      <c r="N57" s="4" t="n">
+      <c r="N59" s="4" t="n">
         <v>6.3</v>
       </c>
-      <c r="O57" s="4" t="n">
+      <c r="O59" s="4" t="n">
         <v>5.94</v>
       </c>
-      <c r="P57" s="2" t="inlineStr">
+      <c r="P59" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/0900-Bora-Bora-BIO-The-noir-aromatise-passion-Bora-Bora-BIO-Teatower_4f2e9195-322a-4284-a012-885b550ea23f.jpg?v=1762729589</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr">
+      <c r="Q59" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/the-noir-aromatise-passion-bora-bora-bio-teatower</t>
         </is>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="R59" s="2" t="inlineStr">
         <is>
           <t>Bora Bora - BIO
 Bora Bora - BIO est un thé noir parfumé biologique aux saveurs exotiques et ensoleillées de pêche, de citronnelle et d’ananas. Évocateur d’évasion et de douceur tropicale, il offre une infusion fruitée et rafraîchissante, idéale pour une dégustation en journée.
@@ -6866,7 +7086,7 @@
 Moment de consommation : Journée</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr">
+      <c r="S59" s="2" t="inlineStr">
         <is>
           <t>Bora Bora - BIO
 Bora Bora - BIO is een biologische gearomatiseerde zwarte thee met exotische en zonnige smaken van perzik, citroengras en ananas. Deze thee roept beelden op van ontsnapping en tropische zachtheid en biedt een fruitige en verfrissende infusie, ideaal voor overdag.
@@ -6888,73 +7108,73 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>V0905</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>5413393807913</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Un Noël Vanillé</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Een Gevanielleerde Kerst</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>100 g vrac</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>Oolong, thé blanc &amp; vert — vanille, amande, pomme</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Oolong, witte &amp; groene thee — vanille, amandel, appel</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="I60" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="4" t="n">
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="L58" s="5" t="n">
+      <c r="L60" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M58" s="4" t="n">
+      <c r="M60" s="4" t="n">
         <v>11.32</v>
       </c>
-      <c r="N58" s="4" t="n">
+      <c r="N60" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="O58" s="4" t="n">
+      <c r="O60" s="4" t="n">
         <v>6.79</v>
       </c>
-      <c r="P58" s="2" t="inlineStr">
+      <c r="P60" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/Un_noel_vanille.png?v=1769590364</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="inlineStr">
+      <c r="Q60" s="2" t="inlineStr">
         <is>
           <t>https://teatower.com/products/un-noel-vanille-oolong-parfume-vanille-teatower</t>
         </is>
       </c>
-      <c r="R58" s="2" t="inlineStr">
+      <c r="R60" s="2" t="inlineStr">
         <is>
           <t>Un Noël Vanillé – Thé Oolong, Blanc &amp; Vert aux Saveurs de Fêtes
 Découvrez Un Noël Vanillé, une infusion raffinée et festive qui marie la douceur de la pomme, la chaleur de la cannelle et la gourmandise de la vanille. Élaborée sur une base de Oolong, de thé blanc et de thé vert, cette création Teatower offre une tasse élégante et délicatement parfumée, parfaite pour les instants cocooning de l’hiver.
@@ -6978,7 +7198,7 @@
 Astuce dégustation : savourez ce thé chaud pour accompagner un dessert de fête, ou froid pour une pause vanillée rafraîchissante. 🎄🍏</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr">
+      <c r="S60" s="2" t="inlineStr">
         <is>
           <t>Un Noël Vanillé – Oolong, Witte &amp; Groene Thee met Feestelijke Smaken
 Ontdek Un Noël Vanillé, een verfijnde en feestelijke infusie die de zoetheid van appel, de warmte van kaneel en de verleidelijke smaak van vanille samenbrengt. Gebaseerd op een blend van Oolong, witte thee en groene thee, biedt deze Teatower-creatie een elegante en delicaat geparfumeerde kop thee, perfect voor knusse wintermomenten.
@@ -7003,69 +7223,180 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>V0913</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>5413393003902</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Féérie d'Hiver</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Wintersprookje</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>100 g vrac</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Infusion de fruits — canneberge, orange</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Vruchteninfusie — veenbes, sinaasappel</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="N61" s="4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O61" s="4" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003902-Feerie-dHiver.jpg?v=1762730488</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>Féérie d’Hiver – Infusion Canneberge &amp; Orange
+Plongez dans Féérie d’Hiver, une infusion fruitée et envoûtante qui marie la douceur des canneberges à la fraîcheur de l’orange et à l’intensité des baies d’hiver. Une boisson festive et sans théine, idéale pour vos instants cocooning durant la saison froide.
+Recette &amp; préparation
+•
+Contenu : vrac 100 Gr
+•
+Dosage : 1–2 c. à café pour 250 ml
+•
+Température : 95 °C
+•
+Infusion : 8–10 minutes
+Ingrédients
+• Grains de raisin huilés (raisins, huile de tournesol)
+• Canneberges entières et sucrées (canneberges, sucre, huile de tournesol)
+• Cristaux de sucre (sucre, farine de riz, matières grasses végétales (colza), fécule de pomme de terre, colorants : E120, E160a, arôme)
+• Baies de sorbier
+• Baies d’argousier
+• Fleurs de bleuet
+• Arôme
+Astuce dégustation : dégustez cette infusion bien chaude pour une pause fruitée et lumineuse, ou ajoutez-en quelques cuillères pour parfumer un vin chaud maison aux notes d’orange et de canneberge. 🍊🍷❄️</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>Wintersprookje – Cranberry &amp; Oranje Infusie (SEO-geoptimaliseerd)
+Dompel jezelf onder in Wintersprookje, een fruitige en betoverende infusie die de zoetheid van cranberries combineert met de frisheid van sinaasappel en de intensiteit van winterbessen. Een feestelijke en theïnevrije drank, ideaal voor jouw cocooning momenten tijdens het koude seizoen.
+Recept &amp; bereiding
+•
+Inhoud: losse thee 100 Gr
+•
+Dosering: 1–2 tl voor 250 ml
+•
+Temperatuur: 95 °C
+•
+Infusie: 8–10 minuten
+Ingrediënten
+• Geoliede rozijnen (rozijnen, zonnebloemolie)
+• Hele en gezoete cranberries (cranberries, suiker, zonnebloemolie)
+• Suikerkristallen (suiker, rijstmeel, plantaardige vetten (koolzaad), aardappelzetmeel, kleurstoffen: E120, E160a, aroma)
+• Lijsterbessen
+• Duindoornbessen
+• Korenbloembloemen
+• Aroma
+Degustatietip: geniet van deze infusie lekker warm voor een fruitige en heldere pauze, of voeg een paar lepels toe om een zelfgemaakte glühwein te parfumeren met tonen van sinaasappel en cranberry. 🍊🍷❄️</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>C0185</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>5413393003858</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>La petite boîte à infusions</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Het kleine infusiedoosje</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Boîte 10 infusettes</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>Coffret 10 infusettes sans théine : vanille-cannelle, cerise-amaretto, menthe-rose-lavande, masala chai, canneberge-orange</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>Doosje 10 theezakjes cafeïnevrij: vanille-kaneel, kers-amaretto, munt-roos-lavendel, masala chai, veenbes-sinaasappel</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="I62" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="4" t="n">
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="L59" s="5" t="n">
+      <c r="L62" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M59" s="4" t="n">
+      <c r="M62" s="4" t="n">
         <v>9.43</v>
       </c>
-      <c r="N59" s="4" t="n">
+      <c r="N62" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O59" s="4" t="n">
+      <c r="O62" s="4" t="n">
         <v>5.66</v>
       </c>
-      <c r="P59" s="2" t="inlineStr">
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003858-La-petite-boite-a-infusions.jpg?v=1762730478</t>
         </is>
       </c>
-      <c r="Q59" s="2" t="inlineStr"/>
-      <c r="R59" s="2" t="inlineStr">
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr">
         <is>
           <t>La Petite Boîte à Infusions — 10 Infusettes
 Petite par la taille, grande par les saveurs. Cette boîte tient dans la paume de la main, mais elle contient cinq voyages : les épices chaudes de l'Inde, la douceur de la Méditerranée, les nuits étoilées d'hiver, les cerises de Venise et le calme d'un jardin de roses. 10 infusettes, 5 univers, zéro théine.
@@ -7078,7 +7409,7 @@
 Le petit cadeau qui fait mouche. Format poche, prix doux, effet garanti. À glisser dans une carte, un sac ou sous le sapin.</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr">
+      <c r="S62" s="2" t="inlineStr">
         <is>
           <t>Het Kleine Infusiedoosje — 10 Theezakjes
 Klein van formaat, groot van smaak. Dit doosje past in je handpalm, maar bevat vijf reizen: de warme kruiden van India, de zachtheid van de Middellandse Zee, de sterrenvolle winternachten, de kersen van Venetië en de rust van een rozentuin. 10 theezakjes, 5 werelden, geen cafeïne.
@@ -7092,69 +7423,69 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>C0186</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>5413393003841</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>La petite boîte à thés</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Het kleine theedoosje</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Boîte 10 infusettes</t>
         </is>
       </c>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>Coffret 10 infusettes de thé : spéculoos, cerise-jasmin, oolong vanille, orange-amande, pomme-cannelle</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Doosje 10 theezakjes thee: speculaas, kers-jasmijn, oolong vanille, sinaasappel-amandel, appel-kaneel</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="I63" s="2" t="n">
         <v>298</v>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="4" t="n">
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="L60" s="5" t="n">
+      <c r="L63" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M60" s="4" t="n">
+      <c r="M63" s="4" t="n">
         <v>9.43</v>
       </c>
-      <c r="N60" s="4" t="n">
+      <c r="N63" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="O60" s="4" t="n">
+      <c r="O63" s="4" t="n">
         <v>5.66</v>
       </c>
-      <c r="P60" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003841-Coffret-cacahuete-The-2025.jpg?v=1762730481</t>
         </is>
       </c>
-      <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="2" t="inlineStr">
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr">
         <is>
           <t>La Petite Boîte à Thés — 10 Infusettes
 Pour ceux qui préfèrent la profondeur du thé à la légèreté de l'infusion. Cette petite boîte réunit cinq thés d'exception — du spéculoos belge à la pâtisserie orientale, en passant par la vanille de Noël et la pomme-cannelle de mamie. 10 sachets, 5 caractères, une seule certitude : vous allez trouver votre favori.
@@ -7167,7 +7498,7 @@
 Un petit prix, un grand effet. À offrir sans raison particulière — ou parce que les meilleurs cadeaux sont ceux qu'on n'attend pas.</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr">
+      <c r="S63" s="2" t="inlineStr">
         <is>
           <t>De Kleine Theedoos — 10 Theezakjes
 Voor wie de diepte van thee verkiest boven de lichtheid van tisanes. Deze kleine doos verenigt vijf uitzonderlijke theeën — van Belgische speculoos tot oosterse patisserie, via kerstvanille en oma's appel-kaneel. 10 zakjes, 5 karakters, één zekerheid: u gaat uw favoriet vinden.
@@ -7181,69 +7512,69 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>C0187</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>5413393003865</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Coffret découverte de Noël</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Kerst ontdekkingsbox</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Coffret 25 infusettes</t>
         </is>
       </c>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>Coffret 25 infusettes : cacao-noisette, rooibos amande, orange-cannelle, oolong vanille, canneberge-orange</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Box 25 theezakjes: cacao-hazelnoot, rooibos amandel, sinaasappel-kaneel, oolong vanille, veenbes-sinaasappel</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
+      <c r="I64" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="4" t="n">
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L61" s="5" t="n">
+      <c r="L64" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M61" s="4" t="n">
+      <c r="M64" s="4" t="n">
         <v>14.15</v>
       </c>
-      <c r="N61" s="4" t="n">
+      <c r="N64" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="O61" s="4" t="n">
+      <c r="O64" s="4" t="n">
         <v>8.49</v>
       </c>
-      <c r="P61" s="2" t="inlineStr">
+      <c r="P64" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003865-Coffret-decouverte-de-Noel-2025.jpg?v=1762730484</t>
         </is>
       </c>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="2" t="inlineStr">
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr">
         <is>
           <t>Coffret Découverte de Noël — 25 Infusettes Festives
 Imaginez : dehors, le froid de décembre. Dedans, vos mains enveloppent une tasse fumante aux parfums de cannelle, de cacao et d'orange confite. Le Coffret Découverte de Noël, c'est ce moment-là — multiplié par 25. Cinq créations Teatower réunies dans un seul coffret, pour transformer chaque matin de décembre en petit rituel gourmand.
@@ -7260,7 +7591,7 @@
 Pour qui ? Pour la personne qui vous dit toujours "rien, merci" quand vous demandez ce qui lui ferait plaisir. Ce coffret, c'est la réponse parfaite.</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr">
+      <c r="S64" s="2" t="inlineStr">
         <is>
           <t>\
 \Kerst Ontdekkingsdoos – 25 Feestelijke Infusettes\
@@ -7297,69 +7628,69 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>C0188</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>5413393003872</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>La hotte de Noël</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>De kerstsok</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Coffret 4 × 50 g + pince</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n"/>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>Coffret 4 × 50 g vrac + pince à thé : cacao-noisette, orange-cannelle, rooibos amande, canneberge-orange</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>Box 4 × 50 g losse thee + theeklem: cacao-hazelnoot, sinaasappel-kaneel, rooibos amandel, veenbes-sinaasappel</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="I65" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="4" t="n">
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="L62" s="5" t="n">
+      <c r="L65" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="M62" s="4" t="n">
+      <c r="M65" s="4" t="n">
         <v>37.74</v>
       </c>
-      <c r="N62" s="4" t="n">
+      <c r="N65" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="O62" s="4" t="n">
+      <c r="O65" s="4" t="n">
         <v>22.64</v>
       </c>
-      <c r="P62" s="2" t="inlineStr">
+      <c r="P65" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003872-La-hotte-de-Noel.jpg?v=1762730486</t>
         </is>
       </c>
-      <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="2" t="inlineStr">
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr">
         <is>
           <t>La Hotte de Noël — Coffret 4 Infusions en Vrac + Pince à Thé
 200 grammes de pur bonheur hivernal. Ouvrez la hotte et laissez les parfums vous envahir : le cacao grillé du Trésor des Lutins, les épices chaudes de l'Offrande des Rois Mages, l'amande douce de la Gourmandise de Noël, et la canneberge pétillante de la Féérie d'Hiver. Quatre boîtes, une pince à thé, des semaines de plaisir.
@@ -7374,7 +7705,7 @@
 Pour les amoureux du vrai thé. Ce coffret est fait pour ceux qui prennent le temps d'infuser, de sentir, de savourer.</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr">
+      <c r="S65" s="2" t="inlineStr">
         <is>
           <t>De Kerstzak — Geschenkset 4 Losse Infusies + Theeklem
 200 gram puur wintergeluk. Open de zak en laat de geuren je overweldigen: de geroosterde cacao van Schat der Kaboutertjes, de warme kruiden van Geschenk der Wijzen, de zoete amandel van Kerstlekkernij, en de sprankelende cranberry van Wintersprookje. Vier doosjes, één theeklem, weken vol genot.
@@ -7390,340 +7721,6 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>C0191</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>5413393004350</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Trésor des lutins</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Schat van de elfen</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Boîte 50 g</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>Infusion de fruits — chocolat, noisette</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>Vruchteninfusie — chocolade, hazelnoot</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M63" s="4" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="N63" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O63" s="4" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003872_3.png?v=1768229545</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>Trésor des Lutins
-Au fond de l'atelier du Père Noël, les lutins cachent un secret. Quand les rires s'estompent et que l'ouvrage avance, ils s'accordent une pause autour d'un bol fumant qui sent la noisette grillée et le cacao. C'est leur trésor, celui qui réchauffe les cœurs avant la grande distribution. Une recette transmise de lutin en lutin, pour les moments où l'on a besoin de croire encore un peu à la magie.
-Dans votre tasse, cette infusion révèle une robe ambrée aux reflets cuivrés. La noisette grillée enveloppe le palais de sa douceur toastée, tandis que le cacao apporte une note chocolatée réconfortante. Les morceaux de pomme acidulés équilibrent cette gourmandise d'hiver, créant une harmonie parfaite entre fruité et torréfié.
-Ingrédients
-• Morceaux de pomme (pomme, acide citrique)
-• Écorces et brisures de cacao
-• Feuilles d'amandier
-• Pétales de rose rouge, bleuet blanc, fleurs de carthame
-• Arôme naturel
-**Ingrédient allergène : amandes.
-Conseils de préparation
-•
-Dosage : 1–2 c. à café pour 250 ml
-•
-Température : 95 °C
-•
-Infusion : 8–10 minutes
-•
-Théine : Sans théine
-•
-Moment idéal : Tout moment de la journée
-Astuce gourmande : Ajoutez une pointe de lait d'amande pour intensifier la note noisette de cette infusion de Noël.</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="inlineStr">
-        <is>
-          <t>Schatt van de Elfen – Kerstinfusie Hazelnoot &amp; Cacao (Theïne Vrij)
-Stap binnen in de betoverende werkplaats van de Kerstman: Schatt van de Elfen combineert de zachtheid van geroosterde hazelnoot met cacao en winterfruit, voor een heerlijke en natuurlijk theïnevrije kerstinfusie.
-Recept &amp; bereiding
-• Inhoud: los 50 Gr
-• Dosering: 1–2 tl voor 250 ml
-• Temperatuur: 95 °C
-• Infusie: 8–10 minuten
-Ingrediënten
-• Stukjes appel (appel, citroenzuur)
-• Cacaoschillen en -gruis
-• Amandelbladeren
-• Rode rozenblaadjes, witte korenbloem, saffloerbloemen
-• Natuurlijk aroma
-**Allergeen ingrediënt: amandelen.
-Tip voor proeven: ideaal op elk moment van de dag voor een zachte en gastronomische pauze.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>C0192</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>5413393004367</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Gourmandise de Noël</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Kerstlekkernij</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Boîte 50 g</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="n"/>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>Rooibos — amande, ananas</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>Rooibos — amandel, ananas</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M64" s="4" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O64" s="4" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003872_4.png?v=1768230036</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>https://teatower.com/products/rooibos-amande-gourmandise-de-noel-teatower-1</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>Gourmandise de Noël – Rooibos Pâte d’Amande &amp; Ananas
-Laissez-vous séduire par Gourmandise de Noël, un rooibos festif mêlant la douceur de la pâte d’amande à la fraîcheur fruitée des morceaux d’ananas. Une infusion sans théine, idéale pour les instants cocooning de l’hiver.
-Recette &amp; préparation
-•
-Contenu : vrac 50 Gr
-•
-Dosage : 1–2 c. à café pour 250 ml
-•
-Température : 95 °C
-•
-Infusion : 7–10 minutes
-Ingrédients
-• Rooibos d’Afrique du Sud (69%)
-• Morceaux d’ananas (sucre de canne, ananas, acide citrique)
-• Arôme
-• Amandes hachées et effilées**
-• Sucre perlé
-**Ingrédient allergène : amandes.
-Astuce dégustation : savourez chaud, accompagné d’un biscuit de Noël, pour une pause douce et gourmande. 🎄</t>
-        </is>
-      </c>
-      <c r="S64" s="2" t="inlineStr">
-        <is>
-          <t>Kerstlekkernij – Rooibos Amandelpasta &amp; Ananas
-Laat u verleiden door Kerstlekkernij, een feestelijke rooibos die de zoetheid van amandelpasta combineert met de fruitige frisheid van ananasstukjes. Een cafeïnevrije infusie, ideaal voor knusse wintermomenten.
-Bereiding
-• Inhoud: 50 gr losse thee
-• Dosering: 1–2 theelepels per 250 ml
-• Temperatuur: 95°C
-• Trektijd: 7–10 minuten
-Ingrediënten
-• Rooibos uit Zuid-Afrika (69%)
-• Ananasstukjes (rietsuiker, ananas, citroenzuur)
-• Aroma
-• Gehakte en gesneden amandelen**
-• Parelsuiker
-**Allergeen: amandelen.
-Degustatietip: geniet warm, samen met een kerstkoekje, voor een zachte en heerlijke pauze. 🎄</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>C0193</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>5413393004374</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Féérie d'Hiver</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Wintersprookje</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Boîte 50 g</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n"/>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>Infusion de fruits — canneberge, orange</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>Vruchteninfusie — veenbes, sinaasappel</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="N65" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O65" s="4" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0761/7586/8243/files/5413393003872_5.png?v=1768229198</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr"/>
-      <c r="R65" s="2" t="inlineStr">
-        <is>
-          <t>Féérie d'Hiver
-Il neige dehors, et dans votre cuisine flotte déjà ce parfum de fête. Vous versez l'eau frémissante sur les canneberges écarlates et les écorces d'orange. Cinq minutes plus tard, votre tasse se pare d'un rouge rubis profond — comme les guirlandes qui ornent déjà le sapin. C'est Noël qui commence, une gorgée à la fois.
-En bouche, l'acidulé des canneberges danse avec la douceur sucrée des raisins, tandis que l'orange apporte sa note pétillante et fraîche. La liqueur rouge intense réchauffe les mains et le cœur, libérant des arômes de fruits d'hiver qui évoquent les marchés de Noël et les soirées au coin du feu.
-Ingrédients
-• Grains de raisin huilés (raisins, huile de tournesol)
-• Canneberges entières et sucrées (canneberges, sucre, huile de tournesol)
-• Cristaux de sucre (sucre, farine de riz, matières grasses végétales (colza), fécule de pomme de terre, colorants : E120, E160a, arôme)
-• Baies de sorbier
-• Baies d'argousier
-• Fleurs de bleuet
-• Arôme
-Conseils de préparation
-•
-Dosage : 1–2 c. à café pour 250 ml
-•
-Température : 95°C
-•
-Infusion : 8–10 minutes
-•
-Théine : Sans théine
-•
-Moment : Idéale pour vos soirées d'hiver
-Astuce gourmande : Ajoutez quelques cuillères de cette infusion dans votre vin chaud maison — les canneberges et l'orange transformeront votre breuvage en véritable élixir de fête.</t>
-        </is>
-      </c>
-      <c r="S65" s="2" t="inlineStr">
-        <is>
-          <t>Féérie d'Hiver
-Het sneeuwt buiten, en in uw keuken hangt al die feestelijke geur. U giet het borrelende water over de scharlakenrode cranberry's en de sinaasappelschillen. Vijf minuten later tooit uw kopje zich in een diep robijnrood — zoals de slingers die al de kerstboom opfleuren. Zo begint Kerstmis, slok voor slok.
-Op de tong danst de zurige frisheid van cranberry's met de zoete zachtheid van rozijnen, terwijl de sinaasappel zijn sprankelende en frisse toets brengt. De intense rode drank verwarmt handen en hart, en laat winterse fruitaroma's vrij die kerst­markten en avonden bij de haard oproepen.
-Ingrediënten
-• Geolied rozijnkorrels (rozijnen, zonnebloemolie)
-• Hele gesuikerde cranberry's (cranberry's, suiker, zonnebloemolie)
-• Suikerkristallen (suiker, rijstmeel, plantaardige vetten (koolzaad), aardappelzetmeel, kleurstoffen: E120, E160a, aroma)
-• Lijsterbessen
-• Duindoornbessen
-• Korenbloemblaadjes
-• Aroma
-Bereidingsadvies
-•
-Dosering: 1–2 tl. voor 250 ml
-•
-Temperatuur: 95°C
-•
-Trektijd: 8–10 minuten
-•
-Cafeïne: Cafeïnevrij
-•
-Moment: Ideaal voor uw winteravonden
-Lekkere tip: Voeg enkele lepels van deze infusie toe aan uw zelfgemaakte glühwein — de cranberry's en sinaasappel transformeren uw drank tot een waar feestelixer.</t>
-        </is>
-      </c>
-    </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
